--- a/Relevance Stuff/relevance_stuff.xlsx
+++ b/Relevance Stuff/relevance_stuff.xlsx
@@ -16942,7 +16942,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-30T12:11:07+00:00</t>
+          <t xml:space="preserve">2026-10-30T13:51:56+00:00</t>
         </is>
       </c>
     </row>

--- a/Relevance Stuff/relevance_stuff.xlsx
+++ b/Relevance Stuff/relevance_stuff.xlsx
@@ -16942,7 +16942,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-30T13:51:56+00:00</t>
+          <t xml:space="preserve">2026-10-30T15:04:13+00:00</t>
         </is>
       </c>
     </row>

--- a/Relevance Stuff/relevance_stuff.xlsx
+++ b/Relevance Stuff/relevance_stuff.xlsx
@@ -16942,7 +16942,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-30T15:04:13+00:00</t>
+          <t xml:space="preserve">2026-10-30T16:13:41+00:00</t>
         </is>
       </c>
     </row>

--- a/Relevance Stuff/relevance_stuff.xlsx
+++ b/Relevance Stuff/relevance_stuff.xlsx
@@ -16942,7 +16942,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-30T16:13:41+00:00</t>
+          <t xml:space="preserve">2026-10-30T17:06:22+00:00</t>
         </is>
       </c>
     </row>

--- a/Relevance Stuff/relevance_stuff.xlsx
+++ b/Relevance Stuff/relevance_stuff.xlsx
@@ -29061,7 +29061,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-30T18:24:09+00:00</t>
+          <t xml:space="preserve">2026-10-30T20:15:31+00:00</t>
         </is>
       </c>
     </row>

--- a/Relevance Stuff/relevance_stuff.xlsx
+++ b/Relevance Stuff/relevance_stuff.xlsx
@@ -29061,7 +29061,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-30T20:15:31+00:00</t>
+          <t xml:space="preserve">2026-10-30T21:29:56+00:00</t>
         </is>
       </c>
     </row>

--- a/Relevance Stuff/relevance_stuff.xlsx
+++ b/Relevance Stuff/relevance_stuff.xlsx
@@ -29061,7 +29061,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-30T21:29:56+00:00</t>
+          <t xml:space="preserve">2026-10-30T22:44:41+00:00</t>
         </is>
       </c>
     </row>

--- a/Relevance Stuff/relevance_stuff.xlsx
+++ b/Relevance Stuff/relevance_stuff.xlsx
@@ -29061,7 +29061,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-30T22:44:41+00:00</t>
+          <t xml:space="preserve">2026-10-31T02:22:57+00:00</t>
         </is>
       </c>
     </row>

--- a/Relevance Stuff/relevance_stuff.xlsx
+++ b/Relevance Stuff/relevance_stuff.xlsx
@@ -21977,71 +21977,71 @@
     </row>
     <row r="24">
       <c r="A24" s="3">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">AI Governance and Geopolitics</t>
+          <t xml:space="preserve">EU-Africa cooperation in research and innovation</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-27</t>
+          <t xml:space="preserve">2026-10-27T12:00Z</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CERRE — Centre on Regulation in Europe</t>
+          <t xml:space="preserve">EU Research &amp; Innovation</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Main A</t>
+          <t xml:space="preserve">Main C</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">C</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">United States; China</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Americas; Asia &amp; Pacific</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transnational R&amp;I and innovation policy; EU-facing technology standards / regulatory alignment</t>
+          <t xml:space="preserve">EU external R&amp;I partnerships / enlargement; Equitable international research partnerships</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business / industry</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Region: United States, China; issue: Transnational R&amp;I and innovation policy, EU-facing technology standards / regulatory alignment</t>
+          <t xml:space="preserve">Region: cross-regional / ABNJ; issue: EU external R&amp;I partnerships / enlargement, Equitable international research partnerships</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Report finds jurisdictions share AI policy objectives but differ in state control and tolerance of private power.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">This may change Europe's relative research and innovation capacity in technologies that increasingly shape geopolitical power.</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">keep</t>
+          <t xml:space="preserve">provisional</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
@@ -22061,12 +22061,12 @@
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CERRE — Centre on Regulation in Europe</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://cerre.eu/wp-content/uploads/2026/05/CERRE_AI-Governance-and-Geopolitics-1.pdf</t>
+          <t xml:space="preserve">https://news.google.com/rss/articles/CBMiqAJBVV95cUxQaWNKNUFoZWJjS0o5dWVrVzJ2ZzhKSWxkSlNxekhJV196N3RzTjNITjNlbFNFbFJtZVg2ekxteVRjN0oyMEpaUlJXRk5URUVzc3czX0RDTDg3QXRPdzJ5VUZtSTlIbmF1Z0JnZXlKNlg0RTZ4aGFfVnVTLWRwQmJOMjlycjRWclBfdGphc2ZNRlNydTRzWENKVnVyRFlJUURGOXBjcHJGdWZXX1BFTlBnOEFfVUJYQzUyQ0FsczYwSDNjOEhwTVBVRjdOSUFjX1N0QUFKb1JDazdfQWs3LVd1d0NrYXNDTktXWVM0NUxHcm9ld1BZeUZHdXFBSkdFcjRXMnhVYk9nSnd4Z2ZCRkNfVy1tcXFoaW9wU05QeDlIWTJBN0hsSVBsdA?oc=5</t>
         </is>
       </c>
     </row>
@@ -22076,17 +22076,17 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Are we ready to handle PV waste? A review of PV recycling regulations in Europe, the United States, China, and India</t>
+          <t xml:space="preserve">AI Governance and Geopolitics</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-05</t>
+          <t xml:space="preserve">2026-05-27</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energy Sustainability and Society</t>
+          <t xml:space="preserve">CERRE — Centre on Regulation in Europe</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
@@ -22101,7 +22101,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">United States; China; India</t>
+          <t xml:space="preserve">United States; China</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
@@ -22111,22 +22111,22 @@
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">EU external R&amp;I partnerships / enlargement</t>
+          <t xml:space="preserve">Transnational R&amp;I and innovation policy; EU-facing technology standards / regulatory alignment</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Business / industry</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Region: United States, China, India; issue: EU external R&amp;I partnerships / enlargement</t>
+          <t xml:space="preserve">Region: United States, China; issue: Transnational R&amp;I and innovation policy, EU-facing technology standards / regulatory alignment</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">The four jurisdictions differ sharply in regulatory readiness for the coming wave of photovoltaic waste.</t>
+          <t xml:space="preserve">Report finds jurisdictions share AI policy objectives but differ in state control and tolerance of private power.</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
@@ -22136,7 +22136,7 @@
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">review</t>
+          <t xml:space="preserve">keep</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
@@ -22146,22 +22146,22 @@
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-14T07:26:39Z</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">worker-b-20260914T062900Z-b105dc9c7d1b</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Umer Shahzad, Cristina Irene Mihai, Ian Marius Peters</t>
+          <t xml:space="preserve">CERRE — Centre on Regulation in Europe</t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://doi.org/10.1186/s13705-026-00595-7</t>
+          <t xml:space="preserve">https://cerre.eu/wp-content/uploads/2026/05/CERRE_AI-Governance-and-Geopolitics-1.pdf</t>
         </is>
       </c>
     </row>
@@ -22171,17 +22171,17 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Japan's security policy under Prime Minister Takaichi</t>
+          <t xml:space="preserve">Are we ready to handle PV waste? A review of PV recycling regulations in Europe, the United States, China, and India</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-03</t>
+          <t xml:space="preserve">2026-08-05</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Finnish Institute of International Affairs</t>
+          <t xml:space="preserve">Energy Sustainability and Society</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
@@ -22196,7 +22196,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">United States; Indonesia; Australia; China</t>
+          <t xml:space="preserve">United States; China; India</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
@@ -22206,7 +22206,7 @@
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Research security / dual use; Australia strategic reorientation to Europe</t>
+          <t xml:space="preserve">EU external R&amp;I partnerships / enlargement</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
@@ -22216,17 +22216,17 @@
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Region: United States, Indonesia, Australia, China; issue: Research security / dual use, Australia strategic reorientation to Europe</t>
+          <t xml:space="preserve">Region: United States, China, India; issue: EU external R&amp;I partnerships / enlargement</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Takaichi is expanding defence exports and dual-use R&amp;D, turning Japan from arms importer into co-producer.</t>
+          <t xml:space="preserve">The four jurisdictions differ sharply in regulatory readiness for the coming wave of photovoltaic waste.</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Japan's move to co-production creates concrete openings for European defence-technology and industrial partnerships.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
@@ -22241,42 +22241,42 @@
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2026-09-14T07:26:39Z</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">worker-b-20260914T062900Z-b105dc9c7d1b</t>
         </is>
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bart Gaens</t>
+          <t xml:space="preserve">Umer Shahzad, Cristina Irene Mihai, Ian Marius Peters</t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://fiia.fi/wp-content/uploads/2026/09/BP441_Japans-security-policy-under-Prime-Minister-Takaichi.pdf</t>
+          <t xml:space="preserve">https://doi.org/10.1186/s13705-026-00595-7</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ukraine within Eureka’s innovation landscape</t>
+          <t xml:space="preserve">Japan's security policy under Prime Minister Takaichi</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-09</t>
+          <t xml:space="preserve">2026-09-03</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">EUREKA</t>
+          <t xml:space="preserve">Finnish Institute of International Affairs</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -22291,17 +22291,17 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ukraine</t>
+          <t xml:space="preserve">United States; Indonesia; Australia; China</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Europe — enlargement</t>
+          <t xml:space="preserve">Americas; Asia &amp; Pacific</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transnational R&amp;I and innovation policy; EU external R&amp;I partnerships / enlargement</t>
+          <t xml:space="preserve">Research security / dual use; Australia strategic reorientation to Europe</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
@@ -22311,22 +22311,22 @@
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Region: Ukraine; issue: Transnational R&amp;I and innovation policy, EU external R&amp;I partnerships / enlargement</t>
+          <t xml:space="preserve">Region: United States, Indonesia, Australia, China; issue: Research security / dual use, Australia strategic reorientation to Europe</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Describes Ukraine's membership since 2006 as a channel for internationalising its research system during war.</t>
+          <t xml:space="preserve">Takaichi is expanding defence exports and dual-use R&amp;D, turning Japan from arms importer into co-producer.</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Japan's move to co-production creates concrete openings for European defence-technology and industrial partnerships.</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">keep</t>
+          <t xml:space="preserve">review</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
@@ -22346,12 +22346,12 @@
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">EUREKA</t>
+          <t xml:space="preserve">Bart Gaens</t>
         </is>
       </c>
       <c r="S27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.eurekanetwork.org/impact/ukraine-within-eurekas-innovation-landscape/</t>
+          <t xml:space="preserve">https://fiia.fi/wp-content/uploads/2026/09/BP441_Japans-security-policy-under-Prime-Minister-Takaichi.pdf</t>
         </is>
       </c>
     </row>
@@ -22361,17 +22361,17 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">EU and North Macedonia hold third Joint Research and Innovation Committee meeting</t>
+          <t xml:space="preserve">Ukraine within Eureka’s innovation landscape</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-23</t>
+          <t xml:space="preserve">2026-03-09</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ERA Portal Austria</t>
+          <t xml:space="preserve">EUREKA</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
@@ -22386,7 +22386,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">North Macedonia</t>
+          <t xml:space="preserve">Ukraine</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
@@ -22406,17 +22406,17 @@
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Region: North Macedonia; issue: Transnational R&amp;I and innovation policy, EU external R&amp;I partnerships / enlargement</t>
+          <t xml:space="preserve">Region: Ukraine; issue: Transnational R&amp;I and innovation policy, EU external R&amp;I partnerships / enlargement</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">The joint R&amp;I committee reviewed Horizon participation, EU initiatives and North Macedonia’s R&amp;I policy updates.</t>
+          <t xml:space="preserve">Describes Ukraine's membership since 2006 as a channel for internationalising its research system during war.</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Joint committees provide the governance channel through which associated-country research cooperation is maintained.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
@@ -22441,12 +22441,12 @@
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ERA Portal Austria</t>
+          <t xml:space="preserve">EUREKA</t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://era.gv.at/news-items/eu-and-north-macedonia-hold-third-joint-research-and-innovation-committee-meeting/</t>
+          <t xml:space="preserve">https://www.eurekanetwork.org/impact/ukraine-within-eurekas-innovation-landscape/</t>
         </is>
       </c>
     </row>
@@ -22456,42 +22456,42 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">EU pursues closer Israel ties on air defense and space</t>
+          <t xml:space="preserve">EU and North Macedonia hold third Joint Research and Innovation Committee meeting</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08T15:00Z</t>
+          <t xml:space="preserve">2026-04-23</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Politico Europe</t>
+          <t xml:space="preserve">ERA Portal Austria</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Main C</t>
+          <t xml:space="preserve">Main A</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">C</t>
+          <t xml:space="preserve">A</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Israel</t>
+          <t xml:space="preserve">North Macedonia</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Middle East</t>
+          <t xml:space="preserve">Europe — enlargement</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Research security / dual use; Transnational R&amp;I and innovation policy</t>
+          <t xml:space="preserve">Transnational R&amp;I and innovation policy; EU external R&amp;I partnerships / enlargement</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
@@ -22501,17 +22501,17 @@
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Region: Israel; issue: Research security / dual use, Transnational R&amp;I and innovation policy</t>
+          <t xml:space="preserve">Region: North Macedonia; issue: Transnational R&amp;I and innovation policy, EU external R&amp;I partnerships / enlargement</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Israel's space agency chief met the EU research and innovation commissioner for talks on AI and robotics.</t>
+          <t xml:space="preserve">The joint R&amp;I committee reviewed Horizon participation, EU initiatives and North Macedonia’s R&amp;I policy updates.</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dual-use technology cooperation is being rebuilt after years of effective EU-Israel disengagement.</t>
+          <t xml:space="preserve">Joint committees provide the governance channel through which associated-country research cooperation is maintained.</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
@@ -22536,57 +22536,57 @@
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">ERA Portal Austria</t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://news.google.com/rss/articles/CBMifEFVX3lxTFBMdlpkQThhcEIxMHVXa2xWQk1Ed0NyLTNicFhzOGFFd0doTjFQZm9md3NuTzlkY0pUQzUtU0FLTm5pRy0wMVZJcUxNNjEzSm5UdGlHNG5XdlNVZXB4cElUQUlka1FpbV9rNXEtREoydWxVV3pWbGdsUUlvd1Q?oc=5</t>
+          <t xml:space="preserve">https://era.gv.at/news-items/eu-and-north-macedonia-hold-third-joint-research-and-innovation-committee-meeting/</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transatlantic cooperation on AI and national security</t>
+          <t xml:space="preserve">EU pursues closer Israel ties on air defense and space</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-09</t>
+          <t xml:space="preserve">2026-09-08T15:00Z</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CERRE — Centre on Regulation in Europe</t>
+          <t xml:space="preserve">Politico Europe</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Main A</t>
+          <t xml:space="preserve">Main C</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">C</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">China</t>
+          <t xml:space="preserve">Israel</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asia &amp; Pacific</t>
+          <t xml:space="preserve">Middle East</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Research security / dual use</t>
+          <t xml:space="preserve">Research security / dual use; Transnational R&amp;I and innovation policy</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
@@ -22596,17 +22596,17 @@
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Region: China; issue: Research security / dual use</t>
+          <t xml:space="preserve">Region: Israel; issue: Research security / dual use, Transnational R&amp;I and innovation policy</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Issue paper identifies US policy uncertainty, European China positions and asymmetric leverage as barriers to deeper AI-security cooperation.</t>
+          <t xml:space="preserve">Israel's space agency chief met the EU research and innovation commissioner for talks on AI and robotics.</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Export controls can constrain European AI competitiveness while creating pressure for pragmatic transatlantic coordination.</t>
+          <t xml:space="preserve">Dual-use technology cooperation is being rebuilt after years of effective EU-Israel disengagement.</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
@@ -22631,12 +22631,12 @@
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Antonio Calcara, Zach Meyers</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://cerre.eu/wp-content/uploads/2026/04/CERRE_Transatlantic-cooperation-on-AI-and-national-security.pdf</t>
+          <t xml:space="preserve">https://news.google.com/rss/articles/CBMifEFVX3lxTFBMdlpkQThhcEIxMHVXa2xWQk1Ed0NyLTNicFhzOGFFd0doTjFQZm9md3NuTzlkY0pUQzUtU0FLTm5pRy0wMVZJcUxNNjEzSm5UdGlHNG5XdlNVZXB4cElUQUlka1FpbV9rNXEtREoydWxVV3pWbGdsUUlvd1Q?oc=5</t>
         </is>
       </c>
     </row>
@@ -22646,17 +22646,17 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Universities as the Next Counterintelligence Battleground in Geopolitical Contests</t>
+          <t xml:space="preserve">Transatlantic cooperation on AI and national security</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-15</t>
+          <t xml:space="preserve">2026-04-09</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Global Policy</t>
+          <t xml:space="preserve">CERRE — Centre on Regulation in Europe</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -22671,12 +22671,12 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">United States; Canada</t>
+          <t xml:space="preserve">China</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Americas</t>
+          <t xml:space="preserve">Asia &amp; Pacific</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
@@ -22686,27 +22686,27 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Universities / research institutions</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Region: United States, Canada; issue: Research security / dual use</t>
+          <t xml:space="preserve">Region: China; issue: Research security / dual use</t>
         </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">The article argues universities face espionage, interference and IP theft and should adapt counterintelligence concepts to research security.</t>
+          <t xml:space="preserve">Issue paper identifies US policy uncertainty, European China positions and asymmetric leverage as barriers to deeper AI-security cooperation.</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">European governments already use research-security frameworks, but the article’s main frame is global.</t>
+          <t xml:space="preserve">Export controls can constrain European AI competitiveness while creating pressure for pragmatic transatlantic coordination.</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">review</t>
+          <t xml:space="preserve">keep</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
@@ -22716,22 +22716,22 @@
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-13T23:35:57Z</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">worker-a-20260913T224815Z-8fd374ecdc27</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brendan Walker-Munro, Sascha‐Dominik Bachmann</t>
+          <t xml:space="preserve">Antonio Calcara, Zach Meyers</t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://doi.org/10.1111/1758-5899.70167</t>
+          <t xml:space="preserve">https://cerre.eu/wp-content/uploads/2026/04/CERRE_Transatlantic-cooperation-on-AI-and-national-security.pdf</t>
         </is>
       </c>
     </row>
@@ -22741,17 +22741,17 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cleantech Innovation, Industrial Decarbonisation and Global Competition - Where the EU stand in the race towards net-zero compar</t>
+          <t xml:space="preserve">Universities as the Next Counterintelligence Battleground in Geopolitical Contests</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-23</t>
+          <t xml:space="preserve">2026-04-15</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">European Parliament</t>
+          <t xml:space="preserve">Global Policy</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -22766,42 +22766,42 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">China</t>
+          <t xml:space="preserve">United States; Canada</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asia &amp; Pacific</t>
+          <t xml:space="preserve">Americas</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">EU external R&amp;I partnerships / enlargement</t>
+          <t xml:space="preserve">Research security / dual use</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Universities / research institutions</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Region: China; issue: EU external R&amp;I partnerships / enlargement</t>
+          <t xml:space="preserve">Region: United States, Canada; issue: Research security / dual use</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">A European Parliament study compares EU, US and Chinese cleantech innovation, manufacturing and deployment.</t>
+          <t xml:space="preserve">The article argues universities face espionage, interference and IP theft and should adapt counterintelligence concepts to research security.</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">It identifies where European innovation strengths do and do not translate into industrial scale.</t>
+          <t xml:space="preserve">European governments already use research-security frameworks, but the article’s main frame is global.</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">keep</t>
+          <t xml:space="preserve">review</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
@@ -22811,42 +22811,42 @@
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2026-09-13T23:35:57Z</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">worker-a-20260913T224815Z-8fd374ecdc27</t>
         </is>
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Brendan Walker-Munro, Sascha‐Dominik Bachmann</t>
         </is>
       </c>
       <c r="S32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://news.google.com/rss/articles/CBMilAFBVV95cUxOTWkwRkprZGk0MVlUUUxEb1FxWHphLTctdVZEZjYycFkyYmdJNDlXazFuRlM5bHhnUjdkNXpuWTNHb1pSN19obExEaFRBRjhoZXpJbHRfbnpnbDE1cTZaSnhQZFJoRm9FSE1aVXg5SU84OUlCWHdGU1pzY09BRjJaTks2NW5Ha2Z4S0w5STc5dmFmTmkw?oc=5</t>
+          <t xml:space="preserve">https://doi.org/10.1111/1758-5899.70167</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Research security as a collective responsibility: empowering universities, enabling Europe</t>
+          <t xml:space="preserve">Cleantech Innovation, Industrial Decarbonisation and Global Competition - Where the EU stand in the race towards net-zero compar</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-10-27</t>
+          <t xml:space="preserve">2026-08-23</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CESAER</t>
+          <t xml:space="preserve">European Parliament</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -22861,37 +22861,37 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">China</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Asia &amp; Pacific</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Research security / dual use; EU external R&amp;I partnerships / enlargement</t>
+          <t xml:space="preserve">EU external R&amp;I partnerships / enlargement</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Universities / research institutions</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Region: cross-regional / ABNJ; issue: Research security / dual use, EU external R&amp;I partnerships / enlargement</t>
+          <t xml:space="preserve">Region: China; issue: EU external R&amp;I partnerships / enlargement</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">The input note combines university practices with requests for proportionate European and national research-security support.</t>
+          <t xml:space="preserve">A European Parliament study compares EU, US and Chinese cleantech innovation, manufacturing and deployment.</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">It argues safeguards work best when researchers and institutions receive capacity, guidance and consistent rules rather than blanket restrictions.</t>
+          <t xml:space="preserve">It identifies where European innovation strengths do and do not translate into industrial scale.</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
@@ -22916,12 +22916,12 @@
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CESAER</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.cesaer.org/publications/input-note-research-security-as-a-collective-responsibility-empowering-universities-enabling-europe/</t>
+          <t xml:space="preserve">https://news.google.com/rss/articles/CBMilAFBVV95cUxOTWkwRkprZGk0MVlUUUxEb1FxWHphLTctdVZEZjYycFkyYmdJNDlXazFuRlM5bHhnUjdkNXpuWTNHb1pSN19obExEaFRBRjhoZXpJbHRfbnpnbDE1cTZaSnhQZFJoRm9FSE1aVXg5SU84OUlCWHdGU1pzY09BRjJaTks2NW5Ha2Z4S0w5STc5dmFmTmkw?oc=5</t>
         </is>
       </c>
     </row>
@@ -22931,27 +22931,27 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Initiative 3.2. Strengthen Research Security</t>
+          <t xml:space="preserve">Research security as a collective responsibility: empowering universities, enabling Europe</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-16</t>
+          <t xml:space="preserve">2025-10-27</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ERA Portal Austria</t>
+          <t xml:space="preserve">CESAER</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Main C</t>
+          <t xml:space="preserve">Main A</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">C</t>
+          <t xml:space="preserve">A</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
@@ -22966,27 +22966,27 @@
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Research security / dual use; Transnational R&amp;I and innovation policy</t>
+          <t xml:space="preserve">Research security / dual use; EU external R&amp;I partnerships / enlargement</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Universities / research institutions; Business / industry</t>
+          <t xml:space="preserve">Universities / research institutions</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Region: cross-regional / ABNJ; issue: Research security / dual use, Transnational R&amp;I and innovation policy</t>
+          <t xml:space="preserve">Region: cross-regional / ABNJ; issue: Research security / dual use, EU external R&amp;I partnerships / enlargement</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Austria’s 2026–2028 ERA plan creates coordination, awareness and risk-management actions for international scientific cooperation.</t>
+          <t xml:space="preserve">The input note combines university practices with requests for proportionate European and national research-security support.</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">The initiative connects EU recommendations with practical risk assessment and capacity building in Austrian research organisations.</t>
+          <t xml:space="preserve">It argues safeguards work best when researchers and institutions receive capacity, guidance and consistent rules rather than blanket restrictions.</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
@@ -23011,12 +23011,12 @@
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ERA Portal Austria</t>
+          <t xml:space="preserve">CESAER</t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://era.gv.at/era/era-in-austria/national-era-action-plan-2026-2028/field-of-action-3/initiative-32-strengthen-research-security/</t>
+          <t xml:space="preserve">https://www.cesaer.org/publications/input-note-research-security-as-a-collective-responsibility-empowering-universities-enabling-europe/</t>
         </is>
       </c>
     </row>
@@ -23026,62 +23026,62 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Artificial Intelligence and Foreign Information Manipulation: Chinese and Russian approaches</t>
+          <t xml:space="preserve">Initiative 3.2. Strengthen Research Security</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-31</t>
+          <t xml:space="preserve">2026-03-16</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hybrid CoE — European Centre of Excellence for Countering Hybrid Threats</t>
+          <t xml:space="preserve">ERA Portal Austria</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Main A</t>
+          <t xml:space="preserve">Main C</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">C</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">China</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asia &amp; Pacific</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">EU external R&amp;I partnerships / enlargement</t>
+          <t xml:space="preserve">Research security / dual use; Transnational R&amp;I and innovation policy</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Universities / research institutions; Business / industry</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Region: China; issue: EU external R&amp;I partnerships / enlargement</t>
+          <t xml:space="preserve">Region: cross-regional / ABNJ; issue: Research security / dual use, Transnational R&amp;I and innovation policy</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">The paper compares how China and Russia use AI for influence operations, data gathering, targeting and content production.</t>
+          <t xml:space="preserve">Austria’s 2026–2028 ERA plan creates coordination, awareness and risk-management actions for international scientific cooperation.</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">AI can scale hostile information operations against European and allied democratic decision-making.</t>
+          <t xml:space="preserve">The initiative connects EU recommendations with practical risk assessment and capacity building in Austrian research organisations.</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
@@ -23106,12 +23106,12 @@
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heidi Hanhijärvi</t>
+          <t xml:space="preserve">ERA Portal Austria</t>
         </is>
       </c>
       <c r="S35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.hybridcoe.fi/wp-content/uploads/2026/03/Artificial-Intelligence-and-Foreign-Information-Manipulation-Hybrid-CoE-Paper-29.pdf</t>
+          <t xml:space="preserve">https://era.gv.at/era/era-in-austria/national-era-action-plan-2026-2028/field-of-action-3/initiative-32-strengthen-research-security/</t>
         </is>
       </c>
     </row>
@@ -23121,37 +23121,37 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALLEA Contributes to High-Level Discussions on the Role of Science in Ukraine’s Recovery</t>
+          <t xml:space="preserve">Artificial Intelligence and Foreign Information Manipulation: Chinese and Russian approaches</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-27</t>
+          <t xml:space="preserve">2026-03-31</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALLEA</t>
+          <t xml:space="preserve">Hybrid CoE — European Centre of Excellence for Countering Hybrid Threats</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Main C</t>
+          <t xml:space="preserve">Main A</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">C</t>
+          <t xml:space="preserve">A</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ukraine</t>
+          <t xml:space="preserve">China</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Europe — enlargement</t>
+          <t xml:space="preserve">Asia &amp; Pacific</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
@@ -23166,17 +23166,17 @@
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Region: Ukraine; issue: EU external R&amp;I partnerships / enlargement</t>
+          <t xml:space="preserve">Region: China; issue: EU external R&amp;I partnerships / enlargement</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">European academies joined the first High-Level Steering Committee and signed the Gdansk Declaration on Ukrainian science.</t>
+          <t xml:space="preserve">The paper compares how China and Russia use AI for influence operations, data gathering, targeting and content production.</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sets a coordinated international framework for rebuilding Ukraine's research system.</t>
+          <t xml:space="preserve">AI can scale hostile information operations against European and allied democratic decision-making.</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
@@ -23201,12 +23201,12 @@
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALLEA</t>
+          <t xml:space="preserve">Heidi Hanhijärvi</t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://allea.org/allea-contributes-to-high-level-discussions-on-the-role-of-science-in-ukraines-recovery/</t>
+          <t xml:space="preserve">https://www.hybridcoe.fi/wp-content/uploads/2026/03/Artificial-Intelligence-and-Foreign-Information-Manipulation-Hybrid-CoE-Paper-29.pdf</t>
         </is>
       </c>
     </row>
@@ -23216,62 +23216,62 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">EU and US critical raw materials strategies: EU-US Explainer</t>
+          <t xml:space="preserve">ALLEA Contributes to High-Level Discussions on the Role of Science in Ukraine’s Recovery</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-07-16T07:00Z</t>
+          <t xml:space="preserve">2026-06-27</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">European Parliament</t>
+          <t xml:space="preserve">ALLEA</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Main A</t>
+          <t xml:space="preserve">Main C</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">C</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Ukraine</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Europe — enlargement</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Critical raw materials × R&amp;I / technology; EU external R&amp;I partnerships / enlargement</t>
+          <t xml:space="preserve">EU external R&amp;I partnerships / enlargement</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business / industry</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Region: cross-regional / ABNJ; issue: Critical raw materials × R&amp;I / technology, EU external R&amp;I partnerships / enlargement</t>
+          <t xml:space="preserve">Region: Ukraine; issue: EU external R&amp;I partnerships / enlargement</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">A European Parliament briefing compares EU and US critical-raw-material strategies, dependencies and policy tools.</t>
+          <t xml:space="preserve">European academies joined the first High-Level Steering Committee and signed the Gdansk Declaration on Ukrainian science.</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">It documents structural supply risks that shape European research, industry and strategic autonomy.</t>
+          <t xml:space="preserve">Sets a coordinated international framework for rebuilding Ukraine's research system.</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
@@ -23296,12 +23296,12 @@
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">ALLEA</t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://news.google.com/rss/articles/CBMifkFVX3lxTFA3d1VZbmNrSnJ1MW5xdnNzdjBBRzMzeTF4VUhMeXdzb3VXeG9yZ2Z1aDdTZEFRZ05JNjFXN0JRMW93a0dtWlI2OG1Jd1hyVTNqaWFEWU9veDZUQzQxLWdIcjUwR1RHRFNZenRyWkUxR1hHaWZieE03MUNzU3FUZw?oc=5</t>
+          <t xml:space="preserve">https://allea.org/allea-contributes-to-high-level-discussions-on-the-role-of-science-in-ukraines-recovery/</t>
         </is>
       </c>
     </row>
@@ -23311,7 +23311,7 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">India starts formal talks on Horizon Europe association</t>
+          <t xml:space="preserve">EU and US critical raw materials strategies: EU-US Explainer</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -23321,52 +23321,52 @@
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Science|Business</t>
+          <t xml:space="preserve">European Parliament</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Main C</t>
+          <t xml:space="preserve">Main A</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">C</t>
+          <t xml:space="preserve">A</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">India</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asia &amp; Pacific</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">EU external R&amp;I partnerships / enlargement</t>
+          <t xml:space="preserve">Critical raw materials × R&amp;I / technology; EU external R&amp;I partnerships / enlargement</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Business / industry</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Region: India; issue: EU external R&amp;I partnerships / enlargement</t>
+          <t xml:space="preserve">Region: cross-regional / ABNJ; issue: Critical raw materials × R&amp;I / technology, EU external R&amp;I partnerships / enlargement</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">The EU and India began formal negotiations on Horizon Europe association after their July Trade and Technology Council meeting.</t>
+          <t xml:space="preserve">A European Parliament briefing compares EU and US critical-raw-material strategies, dependencies and policy tools.</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Association would make Indian researchers directly eligible for EU programme funding in return for a national contribution.</t>
+          <t xml:space="preserve">It documents structural supply risks that shape European research, industry and strategic autonomy.</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
@@ -23396,7 +23396,7 @@
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://news.google.com/rss/articles/CBMiogFBVV95cUxPcmRseE5uVWZkcEplU01GOUlLVjd5djhjQ0xJbTRHTmZTNUh5R0xsRWdGOTF5amsya2JaVDFUZHJWVHV2QlVKNEQ1S3NGT2xlZVJqclZBZGlLS25BaHBDRWVMSlNLMmItMnJPRVVJU1RCSHZCZ2FPVnk2SDUxR29XMExzTWpKajJyN1h1VndlbTFibENUOHpHaGFuMy0taUdMcFE?oc=5</t>
+          <t xml:space="preserve">https://news.google.com/rss/articles/CBMifkFVX3lxTFA3d1VZbmNrSnJ1MW5xdnNzdjBBRzMzeTF4VUhMeXdzb3VXeG9yZ2Z1aDdTZEFRZ05JNjFXN0JRMW93a0dtWlI2OG1Jd1hyVTNqaWFEWU9veDZUQzQxLWdIcjUwR1RHRFNZenRyWkUxR1hHaWZieE03MUNzU3FUZw?oc=5</t>
         </is>
       </c>
     </row>
@@ -23406,12 +23406,12 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Data Corner: Indian participation in Horizon Europe</t>
+          <t xml:space="preserve">India starts formal talks on Horizon Europe association</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-01</t>
+          <t xml:space="preserve">2026-07-16T07:00Z</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
@@ -23456,12 +23456,12 @@
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Indian organisations already participate in Horizon Europe, with €3.4 million in EU funding reported before formal association.</t>
+          <t xml:space="preserve">The EU and India began formal negotiations on Horizon Europe association after their July Trade and Technology Council meeting.</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">The data establish a baseline for how association could change India’s access to EU research funding.</t>
+          <t xml:space="preserve">Association would make Indian researchers directly eligible for EU programme funding in return for a national contribution.</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
@@ -23491,7 +23491,7 @@
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://news.google.com/rss/articles/CBMiqwFBVV95cUxQRVhFMmIxN3AtRkFXelpLaDBYejd0emlMam9sc2FBZWhoTHpHdV90TjNpYTFHc3d4WXo5UmhzUHpKMUpBTFNZMkU0SlRiZWpjSktfZlROVWN2SkI5QXhkbjZCN0ZlYXB6UkptOXoxOElncHZrVmxodEo0SGlSUnVzZmNkcTd5WXpLLVVKSFlVMWpJaWFzVTVxTHhDZzQwRHFOLVJiYUxoTXRkS28?oc=5</t>
+          <t xml:space="preserve">https://news.google.com/rss/articles/CBMiogFBVV95cUxPcmRseE5uVWZkcEplU01GOUlLVjd5djhjQ0xJbTRHTmZTNUh5R0xsRWdGOTF5amsya2JaVDFUZHJWVHV2QlVKNEQ1S3NGT2xlZVJqclZBZGlLS25BaHBDRWVMSlNLMmItMnJPRVVJU1RCSHZCZ2FPVnk2SDUxR29XMExzTWpKajJyN1h1VndlbTFibENUOHpHaGFuMy0taUdMcFE?oc=5</t>
         </is>
       </c>
     </row>
@@ -23501,17 +23501,17 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Belgian-Chinese researcher arrested over suspected theft of chip secrets</t>
+          <t xml:space="preserve">Data Corner: Indian participation in Horizon Europe</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:55Z</t>
+          <t xml:space="preserve">2026-09-01</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Financial Times</t>
+          <t xml:space="preserve">Science|Business</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
@@ -23526,7 +23526,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">China</t>
+          <t xml:space="preserve">India</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
@@ -23546,17 +23546,17 @@
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Region: China; issue: EU external R&amp;I partnerships / enlargement</t>
+          <t xml:space="preserve">Region: India; issue: EU external R&amp;I partnerships / enlargement</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Belgian authorities arrested a semiconductor researcher suspected of misappropriating gallium-nitride technology and trade secrets.</t>
+          <t xml:space="preserve">Indian organisations already participate in Horizon Europe, with €3.4 million in EU funding reported before formal association.</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">The case highlights research-security and intellectual-property risks around European advanced-semiconductor capability.</t>
+          <t xml:space="preserve">The data establish a baseline for how association could change India’s access to EU research funding.</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
@@ -23586,7 +23586,7 @@
       </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://news.google.com/rss/articles/CBMihAFBVV95cUxOZkZIaURhUUM5bW9SczlEWWJtcmx4WUpIbjZnV3VpTHNtUWFhVUw1YndLNzc1Uzl2YmFvcG1zdVlkYUZDalJYdi01dm90WUJlcmUta1BCWHMtcF8xdWNUYUtFcnByRmp1dzVSOWptMHlLNU1zVVdNbjhYOWVpdUJuZXFJeno?oc=5</t>
+          <t xml:space="preserve">https://news.google.com/rss/articles/CBMiqwFBVV95cUxQRVhFMmIxN3AtRkFXelpLaDBYejd0emlMam9sc2FBZWhoTHpHdV90TjNpYTFHc3d4WXo5UmhzUHpKMUpBTFNZMkU0SlRiZWpjSktfZlROVWN2SkI5QXhkbjZCN0ZlYXB6UkptOXoxOElncHZrVmxodEo0SGlSUnVzZmNkcTd5WXpLLVVKSFlVMWpJaWFzVTVxTHhDZzQwRHFOLVJiYUxoTXRkS28?oc=5</t>
         </is>
       </c>
     </row>
@@ -23596,17 +23596,17 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Experts call for a new approach to Neuro-AI governance - European Commission</t>
+          <t xml:space="preserve">Belgian-Chinese researcher arrested over suspected theft of chip secrets</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08T07:00Z</t>
+          <t xml:space="preserve">2026-09-07T15:55Z</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">EU Research &amp; Innovation</t>
+          <t xml:space="preserve">Financial Times</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
@@ -23621,17 +23621,17 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">China</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Asia &amp; Pacific</t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">EU external R&amp;I partnerships / enlargement; EU-facing technology standards / regulatory alignment</t>
+          <t xml:space="preserve">EU external R&amp;I partnerships / enlargement</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
@@ -23641,17 +23641,17 @@
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Region: cross-regional / ABNJ; issue: EU external R&amp;I partnerships / enlargement, EU-facing technology standards / regulatory alignment</t>
+          <t xml:space="preserve">Region: China; issue: EU external R&amp;I partnerships / enlargement</t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">European Group on Ethics in Science and New Technologies issued an infrastructure-focused Neuro-AI governance statement on 8 September 2026. It</t>
+          <t xml:space="preserve">Belgian authorities arrested a semiconductor researcher suspected of misappropriating gallium-nitride technology and trade secrets.</t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">The case highlights research-security and intellectual-property risks around European advanced-semiconductor capability.</t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
@@ -23681,7 +23681,7 @@
       </c>
       <c r="S41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://news.google.com/rss/articles/CBMi2gFBVV95cUxNV25TdUhhYXBTczR1NlhodXZTc0xncTduYlVreTZkQjNBcmNjcG9rLS16TWQ5VklDc3NrYzNnOEVkd2NtdWlaZDVPUEEtZzFaNDB5aVZQcUpBVXFTNzNwbW9BTnpET0FtQlFsZWNtckFKT2hHZFRzeGx5d3NnUVEwRDJaRzZLNVBJUHhCcFdiMGZWVkM2R2xLdjJQTjRnMEFDZktmVWlrTTlrSjIxdkhFa0wtcTVuWW03c1FqTDhyMGMtSG16ejFrOVlIb3RLLVRQU3M4bzAxX3djUQ?oc=5</t>
+          <t xml:space="preserve">https://news.google.com/rss/articles/CBMihAFBVV95cUxOZkZIaURhUUM5bW9SczlEWWJtcmx4WUpIbjZnV3VpTHNtUWFhVUw1YndLNzc1Uzl2YmFvcG1zdVlkYUZDalJYdi01dm90WUJlcmUta1BCWHMtcF8xdWNUYUtFcnByRmp1dzVSOWptMHlLNU1zVVdNbjhYOWVpdUJuZXFJeno?oc=5</t>
         </is>
       </c>
     </row>
@@ -23691,17 +23691,17 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">EU governments to debate a 19-partnership Horizon Europe portfolio</t>
+          <t xml:space="preserve">Experts call for a new approach to Neuro-AI governance - European Commission</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-08T15:40Z</t>
+          <t xml:space="preserve">2026-09-08T07:00Z</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Science|Business</t>
+          <t xml:space="preserve">EU Research &amp; Innovation</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
@@ -23726,7 +23726,7 @@
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transnational R&amp;I and innovation policy; EU external R&amp;I partnerships / enlargement</t>
+          <t xml:space="preserve">EU external R&amp;I partnerships / enlargement; EU-facing technology standards / regulatory alignment</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
@@ -23736,12 +23736,12 @@
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Region: cross-regional / ABNJ; issue: Transnational R&amp;I and innovation policy, EU external R&amp;I partnerships / enlargement</t>
+          <t xml:space="preserve">Region: cross-regional / ABNJ; issue: EU external R&amp;I partnerships / enlargement, EU-facing technology standards / regulatory alignment</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">A proposal for 19 research partnerships was scheduled for member-state negotiations in October 2026.</t>
+          <t xml:space="preserve">European Group on Ethics in Science and New Technologies issued an infrastructure-focused Neuro-AI governance statement on 8 September 2026. It</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
@@ -23776,7 +23776,7 @@
       </c>
       <c r="S42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://news.google.com/rss/articles/CBMiqwFBVV95cUxNa01CaEYwNVB3V3dxelh1LXE2c3lMNFVFNm1OYmEzYXBSZjVVRFJPSnVjUFVaUEtMcjhBekF0RXlacTVTRWxOMzdLMHJvdzVRbWdaanQ3R2JNbzNxaS1heUxiNk5EenFLdy0yZnVCNlFPNWdLUUJLOWJwUXFrR1dZOFlXYXpNeDFRaW9qM1pkQlBtRHhBdEk4bkNTQ1BKbUpLVlNDbUhpQmJ5aUU?oc=5</t>
+          <t xml:space="preserve">https://news.google.com/rss/articles/CBMi2gFBVV95cUxNV25TdUhhYXBTczR1NlhodXZTc0xncTduYlVreTZkQjNBcmNjcG9rLS16TWQ5VklDc3NrYzNnOEVkd2NtdWlaZDVPUEEtZzFaNDB5aVZQcUpBVXFTNzNwbW9BTnpET0FtQlFsZWNtckFKT2hHZFRzeGx5d3NnUVEwRDJaRzZLNVBJUHhCcFdiMGZWVkM2R2xLdjJQTjRnMEFDZktmVWlrTTlrSjIxdkhFa0wtcTVuWW03c1FqTDhyMGMtSG16ejFrOVlIb3RLLVRQU3M4bzAxX3djUQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -23786,27 +23786,27 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Integrating circular economy and policy synergies for cost-efficient lithium-ion battery supply chains</t>
+          <t xml:space="preserve">EU governments to debate a 19-partnership Horizon Europe portfolio</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-16</t>
+          <t xml:space="preserve">2026-10-08T15:40Z</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Clean Technologies and Environmental Policy</t>
+          <t xml:space="preserve">Science|Business</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Main A</t>
+          <t xml:space="preserve">Main C</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">C</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
@@ -23821,7 +23821,7 @@
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Critical raw materials × R&amp;I / technology; Transnational R&amp;I and innovation policy</t>
+          <t xml:space="preserve">Transnational R&amp;I and innovation policy; EU external R&amp;I partnerships / enlargement</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
@@ -23831,22 +23831,22 @@
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Region: cross-regional / ABNJ; issue: Critical raw materials × R&amp;I / technology, Transnational R&amp;I and innovation policy</t>
+          <t xml:space="preserve">Region: cross-regional / ABNJ; issue: Transnational R&amp;I and innovation policy, EU external R&amp;I partnerships / enlargement</t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">A nine-country EU battery study finds recycling, research investment, subsidies and logistics jointly associate with supply-chain cost performance.</t>
+          <t xml:space="preserve">A proposal for 19 research partnerships was scheduled for member-state negotiations in October 2026.</t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Results suggest strategic support can depend on complementary industrial research and circular-economy infrastructure.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">review</t>
+          <t xml:space="preserve">keep</t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
@@ -23856,92 +23856,92 @@
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-21T17:46:38Z</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">worker-b-20261021T171746Z-e44da281e3bc</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">A. K. M. Mohsin, Md. Rashed, Markus Gerschberger, Sayed Farrukh Ahmed, Ladislav Bartuska, Christopher Schwarz, Md. Kamal Uddin</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="S43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://doi.org/10.1007/s10098-026-03613-6</t>
+          <t xml:space="preserve">https://news.google.com/rss/articles/CBMiqwFBVV95cUxNa01CaEYwNVB3V3dxelh1LXE2c3lMNFVFNm1OYmEzYXBSZjVVRFJPSnVjUFVaUEtMcjhBekF0RXlacTVTRWxOMzdLMHJvdzVRbWdaanQ3R2JNbzNxaS1heUxiNk5EenFLdy0yZnVCNlFPNWdLUUJLOWJwUXFrR1dZOFlXYXpNeDFRaW9qM1pkQlBtRHhBdEk4bkNTQ1BKbUpLVlNDbUhpQmJ5aUU?oc=5</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Associated Countries urge EU to keep FP10 open and research-led</t>
+          <t xml:space="preserve">Integrating circular economy and policy synergies for cost-efficient lithium-ion battery supply chains</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-18</t>
+          <t xml:space="preserve">2026-10-16</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ERA Portal Austria</t>
+          <t xml:space="preserve">Clean Technologies and Environmental Policy</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Main C</t>
+          <t xml:space="preserve">Main A</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">C</t>
+          <t xml:space="preserve">A</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Canada</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Americas</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transnational R&amp;I and innovation policy; EU external R&amp;I partnerships / enlargement</t>
+          <t xml:space="preserve">Critical raw materials × R&amp;I / technology; Transnational R&amp;I and innovation policy</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Universities / research institutions</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Region: Canada; issue: Transnational R&amp;I and innovation policy, EU external R&amp;I partnerships / enlargement</t>
+          <t xml:space="preserve">Region: cross-regional / ABNJ; issue: Critical raw materials × R&amp;I / technology, Transnational R&amp;I and innovation policy</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">They demand a research-led Pillar II, an independent ERC and bottom-up Marie Sklodowska-Curie Actions.</t>
+          <t xml:space="preserve">A nine-country EU battery study finds recycling, research investment, subsidies and logistics jointly associate with supply-chain cost performance.</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">The letter targets the Council during the FP10 design phase, when association terms are being set.</t>
+          <t xml:space="preserve">Results suggest strategic support can depend on complementary industrial research and circular-economy infrastructure.</t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">keep</t>
+          <t xml:space="preserve">review</t>
         </is>
       </c>
       <c r="O44" s="3" t="inlineStr">
@@ -23951,37 +23951,37 @@
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2026-10-21T17:46:38Z</t>
         </is>
       </c>
       <c r="Q44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">worker-b-20261021T171746Z-e44da281e3bc</t>
         </is>
       </c>
       <c r="R44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ERA Portal Austria (editorial)</t>
+          <t xml:space="preserve">A. K. M. Mohsin, Md. Rashed, Markus Gerschberger, Sayed Farrukh Ahmed, Ladislav Bartuska, Christopher Schwarz, Md. Kamal Uddin</t>
         </is>
       </c>
       <c r="S44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://era.gv.at/news-items/associated-countries-urge-eu-to-keep-fp10-open-and-research-led/</t>
+          <t xml:space="preserve">https://doi.org/10.1007/s10098-026-03613-6</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">LERU requests safeguards for dual-use research in FP10</t>
+          <t xml:space="preserve">Associated Countries urge EU to keep FP10 open and research-led</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-21</t>
+          <t xml:space="preserve">2026-05-18</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
@@ -23991,47 +23991,47 @@
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Main A</t>
+          <t xml:space="preserve">Main C</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">C</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Canada</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Americas</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Research security / dual use; Transnational R&amp;I and innovation policy; EU-facing technology standards / regulatory alignment</t>
+          <t xml:space="preserve">Transnational R&amp;I and innovation policy; EU external R&amp;I partnerships / enlargement</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Universities / research institutions</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Region: cross-regional / ABNJ; issue: Research security / dual use, Transnational R&amp;I and innovation policy, EU-facing technology standards / regulatory alignment</t>
+          <t xml:space="preserve">Region: Canada; issue: Transnational R&amp;I and innovation policy, EU external R&amp;I partnerships / enlargement</t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">LERU wants clear, targeted dual-use safeguards while preserving frontier research and international scientific cooperation.</t>
+          <t xml:space="preserve">They demand a research-led Pillar II, an independent ERC and bottom-up Marie Sklodowska-Curie Actions.</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overbroad security rules could discourage collaboration and basic research without targeting genuine risks.</t>
+          <t xml:space="preserve">The letter targets the Council during the FP10 design phase, when association terms are being set.</t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
@@ -24056,12 +24056,12 @@
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ERA Portal Austria</t>
+          <t xml:space="preserve">ERA Portal Austria (editorial)</t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://era.gv.at/news-items/leru-urges-safeguards-for-dual-use-research-in-fp10/</t>
+          <t xml:space="preserve">https://era.gv.at/news-items/associated-countries-urge-eu-to-keep-fp10-open-and-research-led/</t>
         </is>
       </c>
     </row>
@@ -24071,17 +24071,17 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">R&amp;I needs to reduce dependencies on critical raw materials through advanced materials in passenger vehicles</t>
+          <t xml:space="preserve">LERU requests safeguards for dual-use research in FP10</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-18</t>
+          <t xml:space="preserve">2026-05-21</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">European Commission, Joint Research Centre (JRC)</t>
+          <t xml:space="preserve">ERA Portal Austria</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
@@ -24106,7 +24106,7 @@
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Critical raw materials × R&amp;I / technology; Transnational R&amp;I and innovation policy; EU external R&amp;I partnerships / enlargement</t>
+          <t xml:space="preserve">Research security / dual use; Transnational R&amp;I and innovation policy; EU-facing technology standards / regulatory alignment</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
@@ -24116,17 +24116,17 @@
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Region: cross-regional / ABNJ; issue: Critical raw materials × R&amp;I / technology, Transnational R&amp;I and innovation policy, EU external R&amp;I partnerships / enlargement</t>
+          <t xml:space="preserve">Region: cross-regional / ABNJ; issue: Research security / dual use, Transnational R&amp;I and innovation policy, EU-facing technology standards / regulatory alignment</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mature alternatives can cut gallium, palladium, beryllium, magnesium and other critical materials in specific car parts; none is universal.</t>
+          <t xml:space="preserve">LERU wants clear, targeted dual-use safeguards while preserving frontier research and international scientific cooperation.</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mature substitutes chiefly need qualification testing and pilot-line access; the findings can inform EU research programming and materials legislation.</t>
+          <t xml:space="preserve">Overbroad security rules could discourage collaboration and basic research without targeting genuine risks.</t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
@@ -24151,37 +24151,37 @@
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fernando Coelho; Awais Ikram; Filipa M. Oliveira; Stefanos Mourdikoudis; David Pennington</t>
+          <t xml:space="preserve">ERA Portal Austria</t>
         </is>
       </c>
       <c r="S46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://publications.jrc.ec.europa.eu/repository/handle/JRC148265?mode=full</t>
+          <t xml:space="preserve">https://era.gv.at/news-items/leru-urges-safeguards-for-dual-use-research-in-fp10/</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Position Paper “Past, present, and future of the European Research &amp; Innovation Framework programmes 2014-2027” | Coimbra</t>
+          <t xml:space="preserve">R&amp;I needs to reduce dependencies on critical raw materials through advanced materials in passenger vehicles</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-01-01</t>
+          <t xml:space="preserve">2026-09-18</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Coimbra Group</t>
+          <t xml:space="preserve">European Commission, Joint Research Centre (JRC)</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Historical</t>
+          <t xml:space="preserve">Main A</t>
         </is>
       </c>
       <c r="F47" s="3" t="inlineStr">
@@ -24201,32 +24201,32 @@
       </c>
       <c r="I47" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">EU external R&amp;I partnerships / enlargement</t>
+          <t xml:space="preserve">Critical raw materials × R&amp;I / technology; Transnational R&amp;I and innovation policy; EU external R&amp;I partnerships / enlargement</t>
         </is>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Universities / research institutions</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Region: cross-regional / ABNJ; issue: EU external R&amp;I partnerships / enlargement</t>
+          <t xml:space="preserve">Region: cross-regional / ABNJ; issue: Critical raw materials × R&amp;I / technology, Transnational R&amp;I and innovation policy, EU external R&amp;I partnerships / enlargement</t>
         </is>
       </c>
       <c r="L47" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">The Coimbra Group reviews Horizon 2020 and Horizon Europe and recommends changes to future programme design.</t>
+          <t xml:space="preserve">Mature alternatives can cut gallium, palladium, beryllium, magnesium and other critical materials in specific car parts; none is universal.</t>
         </is>
       </c>
       <c r="M47" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">University experience can reveal operational programme frictions, though the source represents stakeholder interests.</t>
+          <t xml:space="preserve">Mature substitutes chiefly need qualification testing and pilot-line access; the findings can inform EU research programming and materials legislation.</t>
         </is>
       </c>
       <c r="N47" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">review</t>
+          <t xml:space="preserve">keep</t>
         </is>
       </c>
       <c r="O47" s="3" t="inlineStr">
@@ -24236,22 +24236,22 @@
       </c>
       <c r="P47" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-26T05:34:15Z</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q47" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">worker-b-20260926T041925Z-4706ad515738</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R47" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Fernando Coelho; Awais Ikram; Filipa M. Oliveira; Stefanos Mourdikoudis; David Pennington</t>
         </is>
       </c>
       <c r="S47" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.coimbra-group.eu/wp-content/uploads/Coimbra-Group-Position-Paper-23Feb.pdf</t>
+          <t xml:space="preserve">https://publications.jrc.ec.europa.eu/repository/handle/JRC148265?mode=full</t>
         </is>
       </c>
     </row>
@@ -24261,17 +24261,17 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Critical raw materials, circular economy, sustainable development: EU policy reflections for future research and innovation</t>
+          <t xml:space="preserve">Position Paper “Past, present, and future of the European Research &amp; Innovation Framework programmes 2014-2027” | Coimbra</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-01</t>
+          <t xml:space="preserve">2023-01-01</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Resources, Conservation and Recycling</t>
+          <t xml:space="preserve">Coimbra Group</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
@@ -24296,27 +24296,27 @@
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Critical raw materials × R&amp;I / technology</t>
+          <t xml:space="preserve">EU external R&amp;I partnerships / enlargement</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Universities / research institutions</t>
         </is>
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Region: cross-regional / ABNJ; issue: Critical raw materials × R&amp;I / technology</t>
+          <t xml:space="preserve">Region: cross-regional / ABNJ; issue: EU external R&amp;I partnerships / enlargement</t>
         </is>
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">A JRC perspective evaluates EU circular-economy policy and critical-material recycling needs in strategic technologies.</t>
+          <t xml:space="preserve">The Coimbra Group reviews Horizon 2020 and Horizon Europe and recommends changes to future programme design.</t>
         </is>
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">EU innovation research priorities, material dependencies and circularity of strategic technologies are the focus of the analysis.</t>
+          <t xml:space="preserve">University experience can reveal operational programme frictions, though the source represents stakeholder interests.</t>
         </is>
       </c>
       <c r="N48" s="3" t="inlineStr">
@@ -24331,22 +24331,22 @@
       </c>
       <c r="P48" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-28T13:03:44Z</t>
+          <t xml:space="preserve">2026-09-26T05:34:15Z</t>
         </is>
       </c>
       <c r="Q48" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">worker-a-20261028T124131Z-6ab6d841b916</t>
+          <t xml:space="preserve">worker-b-20260926T041925Z-4706ad515738</t>
         </is>
       </c>
       <c r="R48" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brian Baldassarre; Samuel Carrara</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="S48" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://doi.org/10.1016/j.resconrec.2024.108060</t>
+          <t xml:space="preserve">https://www.coimbra-group.eu/wp-content/uploads/Coimbra-Group-Position-Paper-23Feb.pdf</t>
         </is>
       </c>
     </row>
@@ -24356,22 +24356,22 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Input note 'Clarifying and optimising civil, dual-use and defence research and innovation in future EU funding programmes'</t>
+          <t xml:space="preserve">Critical raw materials, circular economy, sustainable development: EU policy reflections for future research and innovation</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-26</t>
+          <t xml:space="preserve">2025-04-01</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CESAER</t>
+          <t xml:space="preserve">Resources, Conservation and Recycling</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Main A</t>
+          <t xml:space="preserve">Historical</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
@@ -24391,32 +24391,32 @@
       </c>
       <c r="I49" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Research security / dual use</t>
+          <t xml:space="preserve">Critical raw materials × R&amp;I / technology</t>
         </is>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Universities / research institutions</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Region: cross-regional / ABNJ; issue: Research security / dual use</t>
+          <t xml:space="preserve">Region: cross-regional / ABNJ; issue: Critical raw materials × R&amp;I / technology</t>
         </is>
       </c>
       <c r="L49" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">The note sets out concrete proposals for clarifying how civil, dual-use and defence R&amp;I are positioned in EU programmes.</t>
+          <t xml:space="preserve">A JRC perspective evaluates EU circular-economy policy and critical-material recycling needs in strategic technologies.</t>
         </is>
       </c>
       <c r="M49" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shapes how universities can participate in EU defence-adjacent research funding.</t>
+          <t xml:space="preserve">EU innovation research priorities, material dependencies and circularity of strategic technologies are the focus of the analysis.</t>
         </is>
       </c>
       <c r="N49" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">keep</t>
+          <t xml:space="preserve">review</t>
         </is>
       </c>
       <c r="O49" s="3" t="inlineStr">
@@ -24426,22 +24426,22 @@
       </c>
       <c r="P49" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2026-10-28T13:03:44Z</t>
         </is>
       </c>
       <c r="Q49" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">worker-a-20261028T124131Z-6ab6d841b916</t>
         </is>
       </c>
       <c r="R49" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CESAER</t>
+          <t xml:space="preserve">Brian Baldassarre; Samuel Carrara</t>
         </is>
       </c>
       <c r="S49" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.cesaer.org/publications/clarifying-and-optimising-civil-dual-use-and-defence-research-and-innovation-in-future-eu-funding-programmes/</t>
+          <t xml:space="preserve">https://doi.org/10.1016/j.resconrec.2024.108060</t>
         </is>
       </c>
     </row>
@@ -24451,17 +24451,17 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Research security</t>
+          <t xml:space="preserve">Input note 'Clarifying and optimising civil, dual-use and defence research and innovation in future EU funding programmes'</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-19</t>
+          <t xml:space="preserve">2026-03-26</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Research Council of Finland</t>
+          <t xml:space="preserve">CESAER</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
@@ -24491,7 +24491,7 @@
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Universities / research institutions</t>
         </is>
       </c>
       <c r="K50" s="3" t="inlineStr">
@@ -24501,12 +24501,12 @@
       </c>
       <c r="L50" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Finnish law obliges the funder to address research security while preserving researchers' freedom to choose topics.</t>
+          <t xml:space="preserve">The note sets out concrete proposals for clarifying how civil, dual-use and defence R&amp;I are positioned in EU programmes.</t>
         </is>
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Shapes how universities can participate in EU defence-adjacent research funding.</t>
         </is>
       </c>
       <c r="N50" s="3" t="inlineStr">
@@ -24531,12 +24531,12 @@
       </c>
       <c r="R50" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Research Council of Finland</t>
+          <t xml:space="preserve">CESAER</t>
         </is>
       </c>
       <c r="S50" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.aka.fi/en/from-research-to-society/responsible-science/research-security/</t>
+          <t xml:space="preserve">https://www.cesaer.org/publications/clarifying-and-optimising-civil-dual-use-and-defence-research-and-innovation-in-future-eu-funding-programmes/</t>
         </is>
       </c>
     </row>
@@ -24546,12 +24546,12 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Self-assessment of research security</t>
+          <t xml:space="preserve">Research security</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-21</t>
+          <t xml:space="preserve">2026-08-19</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
@@ -24596,12 +24596,12 @@
       </c>
       <c r="L51" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Applications must include a research security appendix; inadequate risk assessment can make an application inadmissible or rejected.</t>
+          <t xml:space="preserve">Finnish law obliges the funder to address research security while preserving researchers' freedom to choose topics.</t>
         </is>
       </c>
       <c r="M51" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Turns research security from guidance into a funding eligibility condition.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="N51" s="3" t="inlineStr">
@@ -24631,7 +24631,7 @@
       </c>
       <c r="S51" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.aka.fi/en/research-funding/apply-for-funding/how-to-apply-for-funding/az-index-of-application-guidelines/research-security/</t>
+          <t xml:space="preserve">https://www.aka.fi/en/from-research-to-society/responsible-science/research-security/</t>
         </is>
       </c>
     </row>
@@ -24641,17 +24641,17 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strategic by design: Making EU development cooperation work for critical raw materials - HCSS</t>
+          <t xml:space="preserve">Self-assessment of research security</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08</t>
+          <t xml:space="preserve">2026-08-21</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">The Hague Centre for Strategic Studies</t>
+          <t xml:space="preserve">Research Council of Finland</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
@@ -24676,7 +24676,7 @@
       </c>
       <c r="I52" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Critical raw materials × R&amp;I / technology</t>
+          <t xml:space="preserve">Research security / dual use</t>
         </is>
       </c>
       <c r="J52" s="3" t="inlineStr">
@@ -24686,17 +24686,17 @@
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Region: cross-regional / ABNJ; issue: Critical raw materials × R&amp;I / technology</t>
+          <t xml:space="preserve">Region: cross-regional / ABNJ; issue: Research security / dual use</t>
         </is>
       </c>
       <c r="L52" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCSS finds EU critical-raw-material partnerships often struggle to convert political agreements into financeable projects.</t>
+          <t xml:space="preserve">Applications must include a research security appendix; inadequate risk assessment can make an application inadmissible or rejected.</t>
         </is>
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Development-cooperation tools could help close feasibility, governance and financing gaps.</t>
+          <t xml:space="preserve">Turns research security from guidance into a funding eligibility condition.</t>
         </is>
       </c>
       <c r="N52" s="3" t="inlineStr">
@@ -24721,12 +24721,12 @@
       </c>
       <c r="R52" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">The Hague Centre for Strategic Studies</t>
+          <t xml:space="preserve">Research Council of Finland</t>
         </is>
       </c>
       <c r="S52" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://hcss.nl/wp-content/uploads/2026/08/Strategic-by-design-HCSS-2026-1.pdf</t>
+          <t xml:space="preserve">https://www.aka.fi/en/research-funding/apply-for-funding/how-to-apply-for-funding/az-index-of-application-guidelines/research-security/</t>
         </is>
       </c>
     </row>
@@ -24736,17 +24736,17 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Research security as part of funding applications ‒ experiences and lessons from the first application round</t>
+          <t xml:space="preserve">Strategic by design: Making EU development cooperation work for critical raw materials - HCSS</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-21</t>
+          <t xml:space="preserve">2026-09-08</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Research Council of Finland</t>
+          <t xml:space="preserve">The Hague Centre for Strategic Studies</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
@@ -24771,7 +24771,7 @@
       </c>
       <c r="I53" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Research security / dual use</t>
+          <t xml:space="preserve">Critical raw materials × R&amp;I / technology</t>
         </is>
       </c>
       <c r="J53" s="3" t="inlineStr">
@@ -24781,17 +24781,17 @@
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Region: cross-regional / ABNJ; issue: Research security / dual use</t>
+          <t xml:space="preserve">Region: cross-regional / ABNJ; issue: Critical raw materials × R&amp;I / technology</t>
         </is>
       </c>
       <c r="L53" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">The Research Council of Finland reports requiring research-security self-assessment in Academy Project and Fellowship calls.</t>
+          <t xml:space="preserve">HCSS finds EU critical-raw-material partnerships often struggle to convert political agreements into financeable projects.</t>
         </is>
       </c>
       <c r="M53" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Application requirements change how research-security risks are considered before public funding is awarded.</t>
+          <t xml:space="preserve">Development-cooperation tools could help close feasibility, governance and financing gaps.</t>
         </is>
       </c>
       <c r="N53" s="3" t="inlineStr">
@@ -24816,12 +24816,12 @@
       </c>
       <c r="R53" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Research Council of Finland</t>
+          <t xml:space="preserve">The Hague Centre for Strategic Studies</t>
         </is>
       </c>
       <c r="S53" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.aka.fi/en/about-the-rcf/whats-new/blog2/2026/research-security-as-part-of-funding-applications--experiences-and-lessons-from-the-first-application-round/</t>
+          <t xml:space="preserve">https://hcss.nl/wp-content/uploads/2026/08/Strategic-by-design-HCSS-2026-1.pdf</t>
         </is>
       </c>
     </row>
@@ -24831,27 +24831,27 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Exclusive: Commission offers three options for cutting back Horizon Europe industrial partnerships</t>
+          <t xml:space="preserve">Research security as part of funding applications ‒ experiences and lessons from the first application round</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-28T21:34Z</t>
+          <t xml:space="preserve">2026-09-21</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Science|Business</t>
+          <t xml:space="preserve">Research Council of Finland</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Main C</t>
+          <t xml:space="preserve">Main A</t>
         </is>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">C</t>
+          <t xml:space="preserve">A</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
@@ -24866,27 +24866,27 @@
       </c>
       <c r="I54" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">EU external R&amp;I partnerships / enlargement</t>
+          <t xml:space="preserve">Research security / dual use</t>
         </is>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business / industry</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Region: cross-regional / ABNJ; issue: EU external R&amp;I partnerships / enlargement</t>
+          <t xml:space="preserve">Region: cross-regional / ABNJ; issue: Research security / dual use</t>
         </is>
       </c>
       <c r="L54" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">The Commission presented options to consolidate Horizon Europe industrial partnerships from 60 to as few as 18.</t>
+          <t xml:space="preserve">The Research Council of Finland reports requiring research-security self-assessment in Academy Project and Fellowship calls.</t>
         </is>
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">The proposal would materially reshape EU industry-research co-programming and funding structures.</t>
+          <t xml:space="preserve">Application requirements change how research-security risks are considered before public funding is awarded.</t>
         </is>
       </c>
       <c r="N54" s="3" t="inlineStr">
@@ -24911,12 +24911,12 @@
       </c>
       <c r="R54" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Research Council of Finland</t>
         </is>
       </c>
       <c r="S54" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://news.google.com/rss/articles/CBMixgFBVV95cUxOemNUSndfajJncHdmLWRpbTZzOGFsYl8zZ09Sd0d2b0hXMDBUZ2pGaFFvVWhpWnpYaXhOUjdEbkJEeUJVZlU4bEZ1Sjl2azl5dmxOb0JkTkdUNDkwSk5KVThCVVJlU0xSVHJ1OGRpNFlLTUdyT3FVWnN2bkpZNWF1emhFQ3lTNVM5VXR0dVRBa2lOTmJmeHM4TUQ0UlliVmRJX1BoY2Nmcl8tWkJBMElRUHd3R1o3NXN0cmQxay1KRXVQa25tbHc?oc=5</t>
+          <t xml:space="preserve">https://www.aka.fi/en/about-the-rcf/whats-new/blog2/2026/research-security-as-part-of-funding-applications--experiences-and-lessons-from-the-first-application-round/</t>
         </is>
       </c>
     </row>
@@ -24926,12 +24926,12 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Data Corner: Number of collaborative grants falls sharply in Horizon Europe</t>
+          <t xml:space="preserve">Exclusive: Commission offers three options for cutting back Horizon Europe industrial partnerships</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-20T08:01Z</t>
+          <t xml:space="preserve">2026-09-28T21:34Z</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
@@ -24966,7 +24966,7 @@
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Business / industry</t>
         </is>
       </c>
       <c r="K55" s="3" t="inlineStr">
@@ -24976,12 +24976,12 @@
       </c>
       <c r="L55" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Science|Business computes 5,271 collaborative Pillar 2 projects and EUR 32.9 billion from the European Commission dashboard in the first two-thirds</t>
+          <t xml:space="preserve">The Commission presented options to consolidate Horizon Europe industrial partnerships from 60 to as few as 18.</t>
         </is>
       </c>
       <c r="M55" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">The proposal would materially reshape EU industry-research co-programming and funding structures.</t>
         </is>
       </c>
       <c r="N55" s="3" t="inlineStr">
@@ -25011,7 +25011,7 @@
       </c>
       <c r="S55" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://news.google.com/rss/articles/CBMixwFBVV95cUxPMXlLMlNkWGlnbXo3RVhONHpXeWp5N1hjaVNrajdNazRud1FHcW9nN3N3TVFUS3pEaHlaMHJIQ21ING9NUXZxbjNUYnJNb2d5UHg1Y0VNT1RhR3Ntc0tJQVlYeWZXT1BhU1k0YVdCcmNRejkybzZnei1zRjRLRXBBZ2RUWm5aakJZNGVrb2hBcm9BTXFUaUFHd2JhdS1vT2hMWG1QN2YwZHV3SnBXQ3RlT000VzY2bHdxejhFMFhmcGMyREl5NE1j?oc=5</t>
+          <t xml:space="preserve">https://news.google.com/rss/articles/CBMixgFBVV95cUxOemNUSndfajJncHdmLWRpbTZzOGFsYl8zZ09Sd0d2b0hXMDBUZ2pGaFFvVWhpWnpYaXhOUjdEbkJEeUJVZlU4bEZ1Sjl2azl5dmxOb0JkTkdUNDkwSk5KVThCVVJlU0xSVHJ1OGRpNFlLTUdyT3FVWnN2bkpZNWF1emhFQ3lTNVM5VXR0dVRBa2lOTmJmeHM4TUQ0UlliVmRJX1BoY2Nmcl8tWkJBMElRUHd3R1o3NXN0cmQxay1KRXVQa25tbHc?oc=5</t>
         </is>
       </c>
     </row>
@@ -25021,17 +25021,17 @@
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Critical Raw Materials: securing Europe’s supply and strategic autonomy | Atualidade | Parlamento Europeu</t>
+          <t xml:space="preserve">Data Corner: Number of collaborative grants falls sharply in Horizon Europe</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-20T11:00Z</t>
+          <t xml:space="preserve">2026-10-20T08:01Z</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">European Parliament</t>
+          <t xml:space="preserve">Science|Business</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
@@ -25056,7 +25056,7 @@
       </c>
       <c r="I56" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Critical raw materials × R&amp;I / technology</t>
+          <t xml:space="preserve">EU external R&amp;I partnerships / enlargement</t>
         </is>
       </c>
       <c r="J56" s="3" t="inlineStr">
@@ -25066,17 +25066,17 @@
       </c>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Region: cross-regional / ABNJ; issue: Critical raw materials × R&amp;I / technology</t>
+          <t xml:space="preserve">Region: cross-regional / ABNJ; issue: EU external R&amp;I partnerships / enlargement</t>
         </is>
       </c>
       <c r="L56" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">European Parliament endorsed draft critical-raw-materials reforms, voting 470 to 83 with 108 abstentions.</t>
+          <t xml:space="preserve">Science|Business computes 5,271 collaborative Pillar 2 projects and EUR 32.9 billion from the European Commission dashboard in the first two-thirds</t>
         </is>
       </c>
       <c r="M56" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Concrete EU industrial technology-input policy reform with a direct innovation and supply-security connection.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="N56" s="3" t="inlineStr">
@@ -25106,77 +25106,77 @@
       </c>
       <c r="S56" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://news.google.com/rss/articles/CBMi0wFBVV95cUxNTlFrR1R3UDM5NzFXdnpldWQtVzhUZ1Y4NnZDMmhmN0g4ZjdZWFJDVy1xRDNtbWtyYVBmV1BCaHZDcWpJbFdrT0xtbzA1Q1pqS1V6Uy1tdUFBUkxHS2ttQjlGVlRib3ZtTU50RHZ0R3o3ZGZteWlqbldkeVRpSEhNYWt6NWFJRVR6dTA2dVpHb2JFbXM0Zk5Sb2l1UExZZi1yQUlST3ptVEVhSE5CZFg5M2FLZTBVVTFUaUQ4VUlULWxkbVhhX3o3am5rbUhIRTdncE1F?oc=5</t>
+          <t xml:space="preserve">https://news.google.com/rss/articles/CBMixwFBVV95cUxPMXlLMlNkWGlnbXo3RVhONHpXeWp5N1hjaVNrajdNazRud1FHcW9nN3N3TVFUS3pEaHlaMHJIQ21ING9NUXZxbjNUYnJNb2d5UHg1Y0VNT1RhR3Ntc0tJQVlYeWZXT1BhU1k0YVdCcmNRejkybzZnei1zRjRLRXBBZ2RUWm5aakJZNGVrb2hBcm9BTXFUaUFHd2JhdS1vT2hMWG1QN2YwZHV3SnBXQ3RlT000VzY2bHdxejhFMFhmcGMyREl5NE1j?oc=5</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Statement by European Research Institute Directors</t>
+          <t xml:space="preserve">Critical Raw Materials: securing Europe’s supply and strategic autonomy | Atualidade | Parlamento Europeu</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-03-22</t>
+          <t xml:space="preserve">2026-10-20T11:00Z</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWP</t>
+          <t xml:space="preserve">European Parliament</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Historical</t>
+          <t xml:space="preserve">Main C</t>
         </is>
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">C</t>
         </is>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">China</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H57" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asia &amp; Pacific</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I57" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Research security / dual use</t>
+          <t xml:space="preserve">Critical raw materials × R&amp;I / technology</t>
         </is>
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Universities / research institutions</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Region: China; issue: Research security / dual use</t>
+          <t xml:space="preserve">Region: cross-regional / ABNJ; issue: Critical raw materials × R&amp;I / technology</t>
         </is>
       </c>
       <c r="L57" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Same joint statement as the FIIA record, published by SWP, protesting Chinese sanctions on European researchers.</t>
+          <t xml:space="preserve">European Parliament endorsed draft critical-raw-materials reforms, voting 470 to 83 with 108 abstentions.</t>
         </is>
       </c>
       <c r="M57" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Duplicate publication across signatories risks counting one statement twice in the corpus.</t>
+          <t xml:space="preserve">Concrete EU industrial technology-input policy reform with a direct innovation and supply-security connection.</t>
         </is>
       </c>
       <c r="N57" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">review</t>
+          <t xml:space="preserve">keep</t>
         </is>
       </c>
       <c r="O57" s="3" t="inlineStr">
@@ -25186,12 +25186,12 @@
       </c>
       <c r="P57" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-16T11:09:09Z</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q57" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">worker-b-20260916T103241Z-d69fa410f5f1</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R57" s="3" t="inlineStr">
@@ -25201,7 +25201,7 @@
       </c>
       <c r="S57" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.swp-berlin.org/presse/detail/statement-by-european-research-institute-directors</t>
+          <t xml:space="preserve">https://news.google.com/rss/articles/CBMi0wFBVV95cUxNTlFrR1R3UDM5NzFXdnpldWQtVzhUZ1Y4NnZDMmhmN0g4ZjdZWFJDVy1xRDNtbWtyYVBmV1BCaHZDcWpJbFdrT0xtbzA1Q1pqS1V6Uy1tdUFBUkxHS2ttQjlGVlRib3ZtTU50RHZ0R3o3ZGZteWlqbldkeVRpSEhNYWt6NWFJRVR6dTA2dVpHb2JFbXM0Zk5Sb2l1UExZZi1yQUlST3ptVEVhSE5CZFg5M2FLZTBVVTFUaUQ4VUlULWxkbVhhX3o3am5rbUhIRTdncE1F?oc=5</t>
         </is>
       </c>
     </row>
@@ -25211,22 +25211,22 @@
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sustainable productivity growth in agriculture: The role of shifts in R&amp;D investments and technology</t>
+          <t xml:space="preserve">Statement by European Research Institute Directors</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-07</t>
+          <t xml:space="preserve">2021-03-22</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Applied Economic Perspectives and Policy (Wiley)</t>
+          <t xml:space="preserve">SWP</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Main A</t>
+          <t xml:space="preserve">Historical</t>
         </is>
       </c>
       <c r="F58" s="3" t="inlineStr">
@@ -25236,42 +25236,42 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brazil; China; India</t>
+          <t xml:space="preserve">China</t>
         </is>
       </c>
       <c r="H58" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Americas; Asia &amp; Pacific</t>
+          <t xml:space="preserve">Asia &amp; Pacific</t>
         </is>
       </c>
       <c r="I58" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">China in Africa / LAC</t>
+          <t xml:space="preserve">Research security / dual use</t>
         </is>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Universities / research institutions</t>
         </is>
       </c>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Region: Brazil, China, India; issue: China in Africa / LAC</t>
+          <t xml:space="preserve">Region: China; issue: Research security / dual use</t>
         </is>
       </c>
       <c r="L58" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Modelling suggests shifting research from yield maximisation to input saving could cut chemical use substantially.</t>
+          <t xml:space="preserve">Same joint statement as the FIIA record, published by SWP, protesting Chinese sanctions on European researchers.</t>
         </is>
       </c>
       <c r="M58" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Duplicate publication across signatories risks counting one statement twice in the corpus.</t>
         </is>
       </c>
       <c r="N58" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">keep</t>
+          <t xml:space="preserve">review</t>
         </is>
       </c>
       <c r="O58" s="3" t="inlineStr">
@@ -25281,22 +25281,22 @@
       </c>
       <c r="P58" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2026-09-16T11:09:09Z</t>
         </is>
       </c>
       <c r="Q58" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">worker-b-20260916T103241Z-d69fa410f5f1</t>
         </is>
       </c>
       <c r="R58" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zuzana Smeets Křístková; Michiel van Dijk; Robert M'Barek; Hans van Meijl; Tomas Ratinger</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="S58" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://publications.jrc.ec.europa.eu/repository/handle/JRC142267</t>
+          <t xml:space="preserve">https://www.swp-berlin.org/presse/detail/statement-by-european-research-institute-directors</t>
         </is>
       </c>
     </row>
@@ -25306,17 +25306,17 @@
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Report shows country participation in European Innovation Ecosystems Programme</t>
+          <t xml:space="preserve">Sustainable productivity growth in agriculture: The role of shifts in R&amp;D investments and technology</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-22</t>
+          <t xml:space="preserve">2026-04-07</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ERA Portal Austria</t>
+          <t xml:space="preserve">Applied Economic Perspectives and Policy (Wiley)</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
@@ -25331,17 +25331,17 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ukraine</t>
+          <t xml:space="preserve">Brazil; China; India</t>
         </is>
       </c>
       <c r="H59" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Europe — enlargement</t>
+          <t xml:space="preserve">Americas; Asia &amp; Pacific</t>
         </is>
       </c>
       <c r="I59" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">EU external R&amp;I partnerships / enlargement</t>
+          <t xml:space="preserve">China in Africa / LAC</t>
         </is>
       </c>
       <c r="J59" s="3" t="inlineStr">
@@ -25351,17 +25351,17 @@
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Region: Ukraine; issue: EU external R&amp;I partnerships / enlargement</t>
+          <t xml:space="preserve">Region: Brazil, China, India; issue: China in Africa / LAC</t>
         </is>
       </c>
       <c r="L59" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">The report compares country participation in European Innovation Ecosystems.</t>
+          <t xml:space="preserve">Modelling suggests shifting research from yield maximisation to input saving could cut chemical use substantially.</t>
         </is>
       </c>
       <c r="M59" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Participation patterns reveal uneven engagement across national innovation ecosystems.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="N59" s="3" t="inlineStr">
@@ -25386,12 +25386,12 @@
       </c>
       <c r="R59" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ERA Portal Austria</t>
+          <t xml:space="preserve">Zuzana Smeets Křístková; Michiel van Dijk; Robert M'Barek; Hans van Meijl; Tomas Ratinger</t>
         </is>
       </c>
       <c r="S59" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://era.gv.at/news-items/report-shows-country-participation-in-european-innovation-ecosystems-programme/</t>
+          <t xml:space="preserve">https://publications.jrc.ec.europa.eu/repository/handle/JRC142267</t>
         </is>
       </c>
     </row>
@@ -25401,17 +25401,17 @@
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overcoming legal barriers for the uptake of innovation procurement in the EU</t>
+          <t xml:space="preserve">Report shows country participation in European Innovation Ecosystems Programme</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-22</t>
+          <t xml:space="preserve">2026-04-22</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Publications Office of the European Union</t>
+          <t xml:space="preserve">ERA Portal Austria</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
@@ -25426,12 +25426,12 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">United States; Canada; China</t>
+          <t xml:space="preserve">Ukraine</t>
         </is>
       </c>
       <c r="H60" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Americas; Asia &amp; Pacific</t>
+          <t xml:space="preserve">Europe — enlargement</t>
         </is>
       </c>
       <c r="I60" s="3" t="inlineStr">
@@ -25446,17 +25446,17 @@
       </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Region: United States, Canada, China; issue: EU external R&amp;I partnerships / enlargement</t>
+          <t xml:space="preserve">Region: Ukraine; issue: EU external R&amp;I partnerships / enlargement</t>
         </is>
       </c>
       <c r="L60" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Report finds European innovation procurement lags other major economies and blames weak incentives in EU law.</t>
+          <t xml:space="preserve">The report compares country participation in European Innovation Ecosystems.</t>
         </is>
       </c>
       <c r="M60" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Participation patterns reveal uneven engagement across national innovation ecosystems.</t>
         </is>
       </c>
       <c r="N60" s="3" t="inlineStr">
@@ -25481,12 +25481,12 @@
       </c>
       <c r="R60" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Directorate-General for Research and Innovation (European Commission); Corvers Procurement Services</t>
+          <t xml:space="preserve">ERA Portal Austria</t>
         </is>
       </c>
       <c r="S60" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://era.gv.at/news-items/new-report-urges-stronger-eu-rules-to-boost-innovation-procurement/</t>
+          <t xml:space="preserve">https://era.gv.at/news-items/report-shows-country-participation-in-european-innovation-ecosystems-programme/</t>
         </is>
       </c>
     </row>
@@ -25496,17 +25496,17 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Europe has produced tech champions: Here is what they can teach us</t>
+          <t xml:space="preserve">Overcoming legal barriers for the uptake of innovation procurement in the EU</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-27</t>
+          <t xml:space="preserve">2026-05-22</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Centre for European Reform</t>
+          <t xml:space="preserve">Publications Office of the European Union</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
@@ -25521,12 +25521,12 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">China</t>
+          <t xml:space="preserve">United States; Canada; China</t>
         </is>
       </c>
       <c r="H61" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asia &amp; Pacific</t>
+          <t xml:space="preserve">Americas; Asia &amp; Pacific</t>
         </is>
       </c>
       <c r="I61" s="3" t="inlineStr">
@@ -25536,22 +25536,22 @@
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business / industry</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Region: China; issue: EU external R&amp;I partnerships / enlargement</t>
+          <t xml:space="preserve">Region: United States, Canada, China; issue: EU external R&amp;I partnerships / enlargement</t>
         </is>
       </c>
       <c r="L61" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Europe has produced genuine tech leaders whose experience should shape competitiveness and innovation policy.</t>
+          <t xml:space="preserve">Report finds European innovation procurement lags other major economies and blames weak incentives in EU law.</t>
         </is>
       </c>
       <c r="M61" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shifts the policy debate from Europe's missing giants to what its successes actually required.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="N61" s="3" t="inlineStr">
@@ -25576,12 +25576,12 @@
       </c>
       <c r="R61" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">James Green</t>
+          <t xml:space="preserve">Directorate-General for Research and Innovation (European Commission); Corvers Procurement Services</t>
         </is>
       </c>
       <c r="S61" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.cer.eu/sites/default/files/JG_tech_success_27.5.26.pdf</t>
+          <t xml:space="preserve">https://era.gv.at/news-items/new-report-urges-stronger-eu-rules-to-boost-innovation-procurement/</t>
         </is>
       </c>
     </row>
@@ -25591,17 +25591,17 @@
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tracking country innovation performance: The Innovation Output Indicator 2025</t>
+          <t xml:space="preserve">Europe has produced tech champions: Here is what they can teach us</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-01</t>
+          <t xml:space="preserve">2026-05-27</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">JRC Publications Repository</t>
+          <t xml:space="preserve">Centre for European Reform</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
@@ -25631,7 +25631,7 @@
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Business / industry</t>
         </is>
       </c>
       <c r="K62" s="3" t="inlineStr">
@@ -25641,12 +25641,12 @@
       </c>
       <c r="L62" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sweden, Ireland and Germany lead the EU; the EU trails the US, Korea and Japan but beats China.</t>
+          <t xml:space="preserve">Europe has produced genuine tech leaders whose experience should shape competitiveness and innovation policy.</t>
         </is>
       </c>
       <c r="M62" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">The indicator feeds DG RTD monitoring of Framework Programme objectives and complements the European Innovation Scoreboard.</t>
+          <t xml:space="preserve">Shifts the policy debate from Europe's missing giants to what its successes actually required.</t>
         </is>
       </c>
       <c r="N62" s="3" t="inlineStr">
@@ -25671,12 +25671,12 @@
       </c>
       <c r="R62" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">BELLO, Michela, RAVANOS, Panagiotis, TESSARIN, Milene</t>
+          <t xml:space="preserve">James Green</t>
         </is>
       </c>
       <c r="S62" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://publications.jrc.ec.europa.eu/repository/handle/JRC145507</t>
+          <t xml:space="preserve">https://www.cer.eu/sites/default/files/JG_tech_success_27.5.26.pdf</t>
         </is>
       </c>
     </row>
@@ -25686,17 +25686,17 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mapping of technology specialisation, complexity and relatedness of the EU and selected global partners</t>
+          <t xml:space="preserve">Tracking country innovation performance: The Innovation Output Indicator 2025</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-02</t>
+          <t xml:space="preserve">2026-06-01</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CEPS</t>
+          <t xml:space="preserve">JRC Publications Repository</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
@@ -25736,12 +25736,12 @@
       </c>
       <c r="L63" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">The EU leads in scientific output but trails the US and China in patenting and venture capital.</t>
+          <t xml:space="preserve">Sweden, Ireland and Germany lead the EU; the EU trails the US, Korea and Japan but beats China.</t>
         </is>
       </c>
       <c r="M63" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Quantifies the gap between European research strength and commercialisation across strategic technologies.</t>
+          <t xml:space="preserve">The indicator feeds DG RTD monitoring of Framework Programme objectives and complements the European Innovation Scoreboard.</t>
         </is>
       </c>
       <c r="N63" s="3" t="inlineStr">
@@ -25766,12 +25766,12 @@
       </c>
       <c r="R63" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pierre-Alexandre Balland, Andrea Renda</t>
+          <t xml:space="preserve">BELLO, Michela, RAVANOS, Panagiotis, TESSARIN, Milene</t>
         </is>
       </c>
       <c r="S63" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://cdn.ceps.eu/wp-content/uploads/2024/09/Code-of-Conduct-CEPS-events.pdf</t>
+          <t xml:space="preserve">https://publications.jrc.ec.europa.eu/repository/handle/JRC145507</t>
         </is>
       </c>
     </row>
@@ -25781,37 +25781,37 @@
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Is Germany benefitting yet from the crisis in US research?</t>
+          <t xml:space="preserve">Mapping of technology specialisation, complexity and relatedness of the EU and selected global partners</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-27T07:00Z</t>
+          <t xml:space="preserve">2026-06-02</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Science|Business</t>
+          <t xml:space="preserve">CEPS</t>
         </is>
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Main C</t>
+          <t xml:space="preserve">Main A</t>
         </is>
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">C</t>
+          <t xml:space="preserve">A</t>
         </is>
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">United States</t>
+          <t xml:space="preserve">China</t>
         </is>
       </c>
       <c r="H64" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Americas</t>
+          <t xml:space="preserve">Asia &amp; Pacific</t>
         </is>
       </c>
       <c r="I64" s="3" t="inlineStr">
@@ -25821,22 +25821,22 @@
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Universities / research institutions</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K64" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Region: United States; issue: EU external R&amp;I partnerships / enlargement</t>
+          <t xml:space="preserve">Region: China; issue: EU external R&amp;I partnerships / enlargement</t>
         </is>
       </c>
       <c r="L64" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">US research uncertainty is increasing interest in German academic jobs and recruitment initiatives.</t>
+          <t xml:space="preserve">The EU leads in scientific output but trails the US and China in patenting and venture capital.</t>
         </is>
       </c>
       <c r="M64" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">The shift may strengthen German talent inflows, though structural career barriers remain.</t>
+          <t xml:space="preserve">Quantifies the gap between European research strength and commercialisation across strategic technologies.</t>
         </is>
       </c>
       <c r="N64" s="3" t="inlineStr">
@@ -25861,12 +25861,12 @@
       </c>
       <c r="R64" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Pierre-Alexandre Balland, Andrea Renda</t>
         </is>
       </c>
       <c r="S64" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://news.google.com/rss/articles/CBMiiwFBVV95cUxPZ0ZrOUpoVzRmZ2ptUndxRVpyTjk0djJiMlJCZzlTT0sxSmo0WnBRQUxtTl90TktnQTg0T0xGd1lGOURyRjNZd18wWklidU5OdVBkRUtfWmUtX084Vkd6dU16MExzVzlEVDNfTm5YSGZPTWNBYnF5QzNFYUhRb0JBLWdsVnhDWUVaWU5R?oc=5</t>
+          <t xml:space="preserve">https://cdn.ceps.eu/wp-content/uploads/2024/09/Code-of-Conduct-CEPS-events.pdf</t>
         </is>
       </c>
     </row>
@@ -25876,17 +25876,17 @@
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Europe must tighten grip on AI supply chain, experts warn</t>
+          <t xml:space="preserve">Is Germany benefitting yet from the crisis in US research?</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-14T02:03Z</t>
+          <t xml:space="preserve">2026-08-27T07:00Z</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Euractiv</t>
+          <t xml:space="preserve">Science|Business</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
@@ -25901,37 +25901,37 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">China</t>
+          <t xml:space="preserve">United States</t>
         </is>
       </c>
       <c r="H65" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asia &amp; Pacific</t>
+          <t xml:space="preserve">Americas</t>
         </is>
       </c>
       <c r="I65" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">EU-facing technology standards / regulatory alignment</t>
+          <t xml:space="preserve">EU external R&amp;I partnerships / enlargement</t>
         </is>
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Universities / research institutions</t>
         </is>
       </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Region: China; issue: EU-facing technology standards / regulatory alignment</t>
+          <t xml:space="preserve">Region: United States; issue: EU external R&amp;I partnerships / enlargement</t>
         </is>
       </c>
       <c r="L65" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">A new expert report urged Europe to expand compute capacity and reduce strategic AI supply-chain dependencies.</t>
+          <t xml:space="preserve">US research uncertainty is increasing interest in German academic jobs and recruitment initiatives.</t>
         </is>
       </c>
       <c r="M65" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Compute ownership and supply-chain control affect Europe’s ability to develop and deploy advanced AI independently.</t>
+          <t xml:space="preserve">The shift may strengthen German talent inflows, though structural career barriers remain.</t>
         </is>
       </c>
       <c r="N65" s="3" t="inlineStr">
@@ -25961,27 +25961,27 @@
       </c>
       <c r="S65" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://news.google.com/rss/articles/CBMikAFBVV95cUxPZEV0SmRDTGhaSkh2MnBPTjBsWjh4VGpLWGFESlYwSklXUUxBVkhIMXdDZGNaR2hZVFE1VXVxV0Q2VlJwYjV0alVxRnVpeERjY3NEMmZkNm91Tk5BYW1QU05DVmpyNGM1ZkN4aUlCLXFzbWNHUHZIZWw4a3V1OVA3cElQQWo2dGRBSzYwZW1DQXo?oc=5</t>
+          <t xml:space="preserve">https://news.google.com/rss/articles/CBMiiwFBVV95cUxPZ0ZrOUpoVzRmZ2ptUndxRVpyTjk0djJiMlJCZzlTT0sxSmo0WnBRQUxtTl90TktnQTg0T0xGd1lGOURyRjNZd18wWklidU5OdVBkRUtfWmUtX084Vkd6dU16MExzVzlEVDNfTm5YSGZPTWNBYnF5QzNFYUhRb0JBLWdsVnhDWUVaWU5R?oc=5</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">EU-China research cooperation limited to ‘targeted areas’</t>
+          <t xml:space="preserve">Europe must tighten grip on AI supply chain, experts warn</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-10T07:00Z</t>
+          <t xml:space="preserve">2026-09-14T02:03Z</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Research Professional News</t>
+          <t xml:space="preserve">Euractiv</t>
         </is>
       </c>
       <c r="E66" s="3" t="inlineStr">
@@ -26006,7 +26006,7 @@
       </c>
       <c r="I66" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transnational R&amp;I and innovation policy</t>
+          <t xml:space="preserve">EU-facing technology standards / regulatory alignment</t>
         </is>
       </c>
       <c r="J66" s="3" t="inlineStr">
@@ -26016,22 +26016,22 @@
       </c>
       <c r="K66" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Region: China; issue: Transnational R&amp;I and innovation policy</t>
+          <t xml:space="preserve">Region: China; issue: EU-facing technology standards / regulatory alignment</t>
         </is>
       </c>
       <c r="L66" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">A new expert report urged Europe to expand compute capacity and reduce strategic AI supply-chain dependencies.</t>
         </is>
       </c>
       <c r="M66" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">This may shift the risk–reward balance of EU–China research, technology and innovation cooperation.</t>
+          <t xml:space="preserve">Compute ownership and supply-chain control affect Europe’s ability to develop and deploy advanced AI independently.</t>
         </is>
       </c>
       <c r="N66" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">provisional</t>
+          <t xml:space="preserve">keep</t>
         </is>
       </c>
       <c r="O66" s="3" t="inlineStr">
@@ -26056,7 +26056,7 @@
       </c>
       <c r="S66" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://news.google.com/rss/articles/CBMixwFBVV95cUxQR1JiOFNtQlZBYUJUUThOYXVYSjFad2h0TG5OSm9ZdDBaY0NrbVk3UkkxUlZJMWFPczJySWd5RmwtYmZsdFE2bS1iOGJnMHFacHBtWE5GUWpqRTN3QXR4SHVtdE1ZRktGY3V6SUc0OWtIQVhSMUp5QVk2ZjE0N29TdFp6ZzgwTmx0aXpkMFpsM2lfb2xrWUtyWXJLY1hlYnRqNEhQWHNZLUhZZThpeklQU3NHWXQ2SGZhNkpmTllLU1JCN1NMU2Jv?oc=5</t>
+          <t xml:space="preserve">https://news.google.com/rss/articles/CBMikAFBVV95cUxPZEV0SmRDTGhaSkh2MnBPTjBsWjh4VGpLWGFESlYwSklXUUxBVkhIMXdDZGNaR2hZVFE1VXVxV0Q2VlJwYjV0alVxRnVpeERjY3NEMmZkNm91Tk5BYW1QU05DVmpyNGM1ZkN4aUlCLXFzbWNHUHZIZWw4a3V1OVA3cElQQWo2dGRBSzYwZW1DQXo?oc=5</t>
         </is>
       </c>
     </row>
@@ -26066,17 +26066,17 @@
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">The 17th EU-China Joint Steering Committee meeting on Science and Technology Cooperation - European Commission</t>
+          <t xml:space="preserve">EU-China research cooperation limited to ‘targeted areas’</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-13T14:31Z</t>
+          <t xml:space="preserve">2026-08-10T07:00Z</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">EU Research &amp; Innovation</t>
+          <t xml:space="preserve">Research Professional News</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
@@ -26116,17 +26116,17 @@
       </c>
       <c r="L67" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">The EU and China held their 17th science-and-technology committee meeting, assessing shared research flagships and priorities.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M67" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">The meeting directly concerns joint research frameworks, researcher mobility and cross-border science cooperation.</t>
+          <t xml:space="preserve">This may shift the risk–reward balance of EU–China research, technology and innovation cooperation.</t>
         </is>
       </c>
       <c r="N67" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">keep</t>
+          <t xml:space="preserve">provisional</t>
         </is>
       </c>
       <c r="O67" s="3" t="inlineStr">
@@ -26151,7 +26151,7 @@
       </c>
       <c r="S67" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://news.google.com/rss/articles/CBMiigJBVV95cUxNbndpTU9lc2hONXNPa2pCMm54Y05ZV1hCcm5BMTUyQ19sRTV4S1lkTGlyZlVNRFRMd2lWS3E3WWdRZ28tOUlXbFVsRU5nTFFvT2xISW8zOWZtSF81R1prcHJVbGVEZFY5YXdpRmxHcG5WT0VkZ2dYYWI0SWdqVVo4YWh4VVdfNkdQdFlTNjk0enltWENEZF92UHRicEhjS1dVNGtZRzhrQ20zQ1l4M0Eyc21kck9JREJzR0ZCTXNlN0FnaDk3NXRoLW1kLWU2Wlc3T1lGcEZ5V09NSzBJSGNYR2RFbWstSERDSm9YVXpSdXZKT1ByUkdsZXdnV3UwR0NwdVRIT3AzY1FGdw?oc=5</t>
+          <t xml:space="preserve">https://news.google.com/rss/articles/CBMixwFBVV95cUxQR1JiOFNtQlZBYUJUUThOYXVYSjFad2h0TG5OSm9ZdDBaY0NrbVk3UkkxUlZJMWFPczJySWd5RmwtYmZsdFE2bS1iOGJnMHFacHBtWE5GUWpqRTN3QXR4SHVtdE1ZRktGY3V6SUc0OWtIQVhSMUp5QVk2ZjE0N29TdFp6ZzgwTmx0aXpkMFpsM2lfb2xrWUtyWXJLY1hlYnRqNEhQWHNZLUhZZThpeklQU3NHWXQ2SGZhNkpmTllLU1JCN1NMU2Jv?oc=5</t>
         </is>
       </c>
     </row>
@@ -26161,17 +26161,17 @@
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Science Europe publishes response to EC consultation on evaluation of the dual-use regulation</t>
+          <t xml:space="preserve">The 17th EU-China Joint Steering Committee meeting on Science and Technology Cooperation - European Commission</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-15</t>
+          <t xml:space="preserve">2026-10-13T14:31Z</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ERA Portal Austria</t>
+          <t xml:space="preserve">EU Research &amp; Innovation</t>
         </is>
       </c>
       <c r="E68" s="3" t="inlineStr">
@@ -26186,17 +26186,17 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">China</t>
         </is>
       </c>
       <c r="H68" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Asia &amp; Pacific</t>
         </is>
       </c>
       <c r="I68" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Research security / dual use; Transnational R&amp;I and innovation policy</t>
+          <t xml:space="preserve">Transnational R&amp;I and innovation policy</t>
         </is>
       </c>
       <c r="J68" s="3" t="inlineStr">
@@ -26206,17 +26206,17 @@
       </c>
       <c r="K68" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Region: cross-regional / ABNJ; issue: Research security / dual use, Transnational R&amp;I and innovation policy</t>
+          <t xml:space="preserve">Region: China; issue: Transnational R&amp;I and innovation policy</t>
         </is>
       </c>
       <c r="L68" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Science Europe issued an October 2026 response to an EU consultation on dual-use controls and research cooperation.</t>
+          <t xml:space="preserve">The EU and China held their 17th science-and-technology committee meeting, assessing shared research flagships and priorities.</t>
         </is>
       </c>
       <c r="M68" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dual-use guidance can affect researchers’ international collaboration and compliance burdens.</t>
+          <t xml:space="preserve">The meeting directly concerns joint research frameworks, researcher mobility and cross-border science cooperation.</t>
         </is>
       </c>
       <c r="N68" s="3" t="inlineStr">
@@ -26241,12 +26241,12 @@
       </c>
       <c r="R68" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ERA Portal Austria</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="S68" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://era.gv.at/news-items/science-europe-publishes-response-to-ec-consultation-on-evaluation-of-the-dual-use-regulation/</t>
+          <t xml:space="preserve">https://news.google.com/rss/articles/CBMiigJBVV95cUxNbndpTU9lc2hONXNPa2pCMm54Y05ZV1hCcm5BMTUyQ19sRTV4S1lkTGlyZlVNRFRMd2lWS3E3WWdRZ28tOUlXbFVsRU5nTFFvT2xISW8zOWZtSF81R1prcHJVbGVEZFY5YXdpRmxHcG5WT0VkZ2dYYWI0SWdqVVo4YWh4VVdfNkdQdFlTNjk0enltWENEZF92UHRicEhjS1dVNGtZRzhrQ20zQ1l4M0Eyc21kck9JREJzR0ZCTXNlN0FnaDk3NXRoLW1kLWU2Wlc3T1lGcEZ5V09NSzBJSGNYR2RFbWstSERDSm9YVXpSdXZKT1ByUkdsZXdnV3UwR0NwdVRIT3AzY1FGdw?oc=5</t>
         </is>
       </c>
     </row>
@@ -26256,27 +26256,27 @@
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Deep dive on critical raw materials for hydrogen technologies in the EU</t>
+          <t xml:space="preserve">Science Europe publishes response to EC consultation on evaluation of the dual-use regulation</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-20</t>
+          <t xml:space="preserve">2026-10-15</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">JRC Publications Repository</t>
+          <t xml:space="preserve">ERA Portal Austria</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Main A</t>
+          <t xml:space="preserve">Main C</t>
         </is>
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">C</t>
         </is>
       </c>
       <c r="G69" s="3" t="inlineStr">
@@ -26291,7 +26291,7 @@
       </c>
       <c r="I69" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Critical raw materials × R&amp;I / technology; EU external R&amp;I partnerships / enlargement</t>
+          <t xml:space="preserve">Research security / dual use; Transnational R&amp;I and innovation policy</t>
         </is>
       </c>
       <c r="J69" s="3" t="inlineStr">
@@ -26301,17 +26301,17 @@
       </c>
       <c r="K69" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Region: cross-regional / ABNJ; issue: Critical raw materials × R&amp;I / technology, EU external R&amp;I partnerships / enlargement</t>
+          <t xml:space="preserve">Region: cross-regional / ABNJ; issue: Research security / dual use, Transnational R&amp;I and innovation policy</t>
         </is>
       </c>
       <c r="L69" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">EU JRC models 2030-2050 material-supply vulnerabilities for hydrogen technologies; iridium/platinum bottlenecks are scenario-based, not observations.</t>
+          <t xml:space="preserve">Science Europe issued an October 2026 response to an EU consultation on dual-use controls and research cooperation.</t>
         </is>
       </c>
       <c r="M69" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Dual-use guidance can affect researchers’ international collaboration and compliance burdens.</t>
         </is>
       </c>
       <c r="N69" s="3" t="inlineStr">
@@ -26336,32 +26336,32 @@
       </c>
       <c r="R69" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">BOLARD, Julien, NOHL, Markus, PAVEL, Claudiu, ISTRATE, Robert, EYNARD, Umberto, BLAGOEVA, Darina, DOLCI, Francesco, KUZOV, Teodor</t>
+          <t xml:space="preserve">ERA Portal Austria</t>
         </is>
       </c>
       <c r="S69" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://publications.jrc.ec.europa.eu/repository/handle/JRC148105</t>
+          <t xml:space="preserve">https://era.gv.at/news-items/science-europe-publishes-response-to-ec-consultation-on-evaluation-of-the-dual-use-regulation/</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Connecting European Science: ESF Joins Horizon Europe Initiatives to Streamline Research Infrastructure Access - ESF</t>
+          <t xml:space="preserve">Deep dive on critical raw materials for hydrogen technologies in the EU</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-10</t>
+          <t xml:space="preserve">2026-10-20</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">European Science Foundation</t>
+          <t xml:space="preserve">JRC Publications Repository</t>
         </is>
       </c>
       <c r="E70" s="3" t="inlineStr">
@@ -26386,27 +26386,27 @@
       </c>
       <c r="I70" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">EU external R&amp;I partnerships / enlargement</t>
+          <t xml:space="preserve">Critical raw materials × R&amp;I / technology; EU external R&amp;I partnerships / enlargement</t>
         </is>
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business / industry</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K70" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Region: cross-regional / ABNJ; issue: EU external R&amp;I partnerships / enlargement</t>
+          <t xml:space="preserve">Region: cross-regional / ABNJ; issue: Critical raw materials × R&amp;I / technology, EU external R&amp;I partnerships / enlargement</t>
         </is>
       </c>
       <c r="L70" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Access2Access, FUND-RI and COORDINA-INNOV address facility access, sustainable funding and research-infrastructure collaboration with industry.</t>
+          <t xml:space="preserve">EU JRC models 2030-2050 material-supply vulnerabilities for hydrogen technologies; iridium/platinum bottlenecks are scenario-based, not observations.</t>
         </is>
       </c>
       <c r="M70" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Together they target structural fragmentation across Europe’s research-infrastructure ecosystem.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="N70" s="3" t="inlineStr">
@@ -26431,12 +26431,12 @@
       </c>
       <c r="R70" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ines AZAIEZ</t>
+          <t xml:space="preserve">BOLARD, Julien, NOHL, Markus, PAVEL, Claudiu, ISTRATE, Robert, EYNARD, Umberto, BLAGOEVA, Darina, DOLCI, Francesco, KUZOV, Teodor</t>
         </is>
       </c>
       <c r="S70" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.esf.org/esf-joins-horizon-europe-initiatives-to-streamline-research-infrastructure-access/</t>
+          <t xml:space="preserve">https://publications.jrc.ec.europa.eu/repository/handle/JRC148105</t>
         </is>
       </c>
     </row>
@@ -26446,27 +26446,27 @@
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">EU research and innovation funding expands to defence and dual-use technologies</t>
+          <t xml:space="preserve">Connecting European Science: ESF Joins Horizon Europe Initiatives to Streamline Research Infrastructure Access - ESF</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-24</t>
+          <t xml:space="preserve">2026-06-10</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ERA Portal Austria</t>
+          <t xml:space="preserve">European Science Foundation</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Main C</t>
+          <t xml:space="preserve">Main A</t>
         </is>
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">C</t>
+          <t xml:space="preserve">A</t>
         </is>
       </c>
       <c r="G71" s="3" t="inlineStr">
@@ -26481,27 +26481,27 @@
       </c>
       <c r="I71" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Research security / dual use</t>
+          <t xml:space="preserve">EU external R&amp;I partnerships / enlargement</t>
         </is>
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Business / industry</t>
         </is>
       </c>
       <c r="K71" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Region: cross-regional / ABNJ; issue: Research security / dual use</t>
+          <t xml:space="preserve">Region: cross-regional / ABNJ; issue: EU external R&amp;I partnerships / enlargement</t>
         </is>
       </c>
       <c r="L71" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">The 2026 EIC programme now allows dual-use and defence applicants and adds a €100 million defence scale-up call.</t>
+          <t xml:space="preserve">Access2Access, FUND-RI and COORDINA-INNOV address facility access, sustainable funding and research-infrastructure collaboration with industry.</t>
         </is>
       </c>
       <c r="M71" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">The amendment changes eligibility and financing channels, directly expanding EU support for strategic technology scale-up.</t>
+          <t xml:space="preserve">Together they target structural fragmentation across Europe’s research-infrastructure ecosystem.</t>
         </is>
       </c>
       <c r="N71" s="3" t="inlineStr">
@@ -26526,12 +26526,12 @@
       </c>
       <c r="R71" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ERA Portal Austria</t>
+          <t xml:space="preserve">Ines AZAIEZ</t>
         </is>
       </c>
       <c r="S71" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://era.gv.at/news-items/eu-research-and-innovation-funding-expands-to-defence-and-dual-use-technologies/</t>
+          <t xml:space="preserve">https://www.esf.org/esf-joins-horizon-europe-initiatives-to-streamline-research-infrastructure-access/</t>
         </is>
       </c>
     </row>
@@ -26541,12 +26541,12 @@
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">The Guild urges safeguards as FP10 opens to dual-use research</t>
+          <t xml:space="preserve">EU research and innovation funding expands to defence and dual-use technologies</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-07-01</t>
+          <t xml:space="preserve">2026-06-24</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
@@ -26556,12 +26556,12 @@
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Main A</t>
+          <t xml:space="preserve">Main C</t>
         </is>
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">C</t>
         </is>
       </c>
       <c r="G72" s="3" t="inlineStr">
@@ -26581,7 +26581,7 @@
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Universities / research institutions</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K72" s="3" t="inlineStr">
@@ -26591,12 +26591,12 @@
       </c>
       <c r="L72" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">The Guild argues dual-use research needs targeted safeguards without weakening open frontier research.</t>
+          <t xml:space="preserve">The 2026 EIC programme now allows dual-use and defence applicants and adds a €100 million defence scale-up call.</t>
         </is>
       </c>
       <c r="M72" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Broad restrictions could damage basic research and international collaboration.</t>
+          <t xml:space="preserve">The amendment changes eligibility and financing channels, directly expanding EU support for strategic technology scale-up.</t>
         </is>
       </c>
       <c r="N72" s="3" t="inlineStr">
@@ -26626,7 +26626,7 @@
       </c>
       <c r="S72" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://era.gv.at/news-items/the-guild-urges-safeguards-as-fp10-opens-to-dual-use-research/</t>
+          <t xml:space="preserve">https://era.gv.at/news-items/eu-research-and-innovation-funding-expands-to-defence-and-dual-use-technologies/</t>
         </is>
       </c>
     </row>
@@ -26636,12 +26636,12 @@
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">European Innovation Act should put universities at the heart of innovation, EUA says</t>
+          <t xml:space="preserve">The Guild urges safeguards as FP10 opens to dual-use research</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-07-06</t>
+          <t xml:space="preserve">2026-07-01</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
@@ -26671,27 +26671,27 @@
       </c>
       <c r="I73" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">EU external R&amp;I partnerships / enlargement</t>
+          <t xml:space="preserve">Research security / dual use</t>
         </is>
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Universities / research institutions; Business / industry</t>
+          <t xml:space="preserve">Universities / research institutions</t>
         </is>
       </c>
       <c r="K73" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Region: cross-regional / ABNJ; issue: EU external R&amp;I partnerships / enlargement</t>
+          <t xml:space="preserve">Region: cross-regional / ABNJ; issue: Research security / dual use</t>
         </is>
       </c>
       <c r="L73" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">EUA argues the Act should build a shared European innovation culture with universities at its core.</t>
+          <t xml:space="preserve">The Guild argues dual-use research needs targeted safeguards without weakening open frontier research.</t>
         </is>
       </c>
       <c r="M73" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">The Act would be the first EU law focused solely on innovation.</t>
+          <t xml:space="preserve">Broad restrictions could damage basic research and international collaboration.</t>
         </is>
       </c>
       <c r="N73" s="3" t="inlineStr">
@@ -26721,7 +26721,7 @@
       </c>
       <c r="S73" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://era.gv.at/news-items/european-innovation-act-should-put-universities-at-the-heart-of-innovation-eua-says/</t>
+          <t xml:space="preserve">https://era.gv.at/news-items/the-guild-urges-safeguards-as-fp10-opens-to-dual-use-research/</t>
         </is>
       </c>
     </row>
@@ -26731,27 +26731,27 @@
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">EU's cybersecurity agency granted access to Mythos 5 AI model, Commission says</t>
+          <t xml:space="preserve">European Innovation Act should put universities at the heart of innovation, EUA says</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-10T08:56Z</t>
+          <t xml:space="preserve">2026-07-06</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reuters</t>
+          <t xml:space="preserve">ERA Portal Austria</t>
         </is>
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Main C</t>
+          <t xml:space="preserve">Main A</t>
         </is>
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">C</t>
+          <t xml:space="preserve">A</t>
         </is>
       </c>
       <c r="G74" s="3" t="inlineStr">
@@ -26766,27 +26766,27 @@
       </c>
       <c r="I74" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">EU-facing technology standards / regulatory alignment</t>
+          <t xml:space="preserve">EU external R&amp;I partnerships / enlargement</t>
         </is>
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Universities / research institutions; Business / industry</t>
         </is>
       </c>
       <c r="K74" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Region: cross-regional / ABNJ; issue: EU-facing technology standards / regulatory alignment</t>
+          <t xml:space="preserve">Region: cross-regional / ABNJ; issue: EU external R&amp;I partnerships / enlargement</t>
         </is>
       </c>
       <c r="L74" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">The EU cybersecurity agency received access to leading AI models to assess cybersecurity implications.</t>
+          <t xml:space="preserve">EUA argues the Act should build a shared European innovation culture with universities at its core.</t>
         </is>
       </c>
       <c r="M74" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direct model access enables independent security testing and evidence for European AI and cyber-risk governance.</t>
+          <t xml:space="preserve">The Act would be the first EU law focused solely on innovation.</t>
         </is>
       </c>
       <c r="N74" s="3" t="inlineStr">
@@ -26811,12 +26811,12 @@
       </c>
       <c r="R74" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">ERA Portal Austria</t>
         </is>
       </c>
       <c r="S74" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://news.google.com/rss/articles/CBMivAFBVV95cUxPRWVkQ1I1dzB2Wm10ZmloY0d5bW9PNEpSSnVTT0V5bHU0SXNsMnEyY1c0V2NmVnhzSm1qZ0JXZ1dsaHBDNkJmRXdzaWVaeks5ekhROVF0SjU3cGQ5VWRPc1NPRFd2UmtYRTJPZWVLamFvRjV0WmRnWk04UW13UUcwZnlGNFlORzd2cFUxZ056UkRJcEJaekZSMFM3MjREMHpzcWQybWVpTGZkSGZGOGNCQnV3bFowZ3dxeXl2bw?oc=5</t>
+          <t xml:space="preserve">https://era.gv.at/news-items/european-innovation-act-should-put-universities-at-the-heart-of-innovation-eua-says/</t>
         </is>
       </c>
     </row>
@@ -26826,27 +26826,27 @@
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">R&amp;I needs to reduce dependencies on critical raw materials through advanced materials in electronics</t>
+          <t xml:space="preserve">EU's cybersecurity agency granted access to Mythos 5 AI model, Commission says</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-21</t>
+          <t xml:space="preserve">2026-09-10T08:56Z</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">JRC Publications Repository</t>
+          <t xml:space="preserve">Reuters</t>
         </is>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Main A</t>
+          <t xml:space="preserve">Main C</t>
         </is>
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">C</t>
         </is>
       </c>
       <c r="G75" s="3" t="inlineStr">
@@ -26861,7 +26861,7 @@
       </c>
       <c r="I75" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Critical raw materials × R&amp;I / technology</t>
+          <t xml:space="preserve">EU-facing technology standards / regulatory alignment</t>
         </is>
       </c>
       <c r="J75" s="3" t="inlineStr">
@@ -26871,17 +26871,17 @@
       </c>
       <c r="K75" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Region: cross-regional / ABNJ; issue: Critical raw materials × R&amp;I / technology</t>
+          <t xml:space="preserve">Region: cross-regional / ABNJ; issue: EU-facing technology standards / regulatory alignment</t>
         </is>
       </c>
       <c r="L75" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">JRC assesses 74 substitution, design, process, packaging and circularity options across five critical-material portfolios.</t>
+          <t xml:space="preserve">The EU cybersecurity agency received access to leading AI models to assess cybersecurity implications.</t>
         </is>
       </c>
       <c r="M75" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Deployment bottlenecks identify where European R&amp;I capacity and infrastructure are needed.</t>
+          <t xml:space="preserve">Direct model access enables independent security testing and evidence for European AI and cyber-risk governance.</t>
         </is>
       </c>
       <c r="N75" s="3" t="inlineStr">
@@ -26906,12 +26906,12 @@
       </c>
       <c r="R75" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">COELHO, Fernando, OLIVEIRA, Filipa M., MOURDIKOUDIS, Stefanos, PENNINGTON, David</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="S75" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://publications.jrc.ec.europa.eu/repository/handle/JRC147525?mode=full</t>
+          <t xml:space="preserve">https://news.google.com/rss/articles/CBMivAFBVV95cUxPRWVkQ1I1dzB2Wm10ZmloY0d5bW9PNEpSSnVTT0V5bHU0SXNsMnEyY1c0V2NmVnhzSm1qZ0JXZ1dsaHBDNkJmRXdzaWVaeks5ekhROVF0SjU3cGQ5VWRPc1NPRFd2UmtYRTJPZWVLamFvRjV0WmRnWk04UW13UUcwZnlGNFlORzd2cFUxZ056UkRJcEJaekZSMFM3MjREMHpzcWQybWVpTGZkSGZGOGNCQnV3bFowZ3dxeXl2bw?oc=5</t>
         </is>
       </c>
     </row>
@@ -26921,17 +26921,17 @@
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Detecting and responding to cybersecurity incidents - Publications Office of the EU</t>
+          <t xml:space="preserve">R&amp;I needs to reduce dependencies on critical raw materials through advanced materials in electronics</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-22</t>
+          <t xml:space="preserve">2026-09-21</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">EU Publications Office</t>
+          <t xml:space="preserve">JRC Publications Repository</t>
         </is>
       </c>
       <c r="E76" s="3" t="inlineStr">
@@ -26956,7 +26956,7 @@
       </c>
       <c r="I76" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">EU-facing technology standards / regulatory alignment</t>
+          <t xml:space="preserve">Critical raw materials × R&amp;I / technology</t>
         </is>
       </c>
       <c r="J76" s="3" t="inlineStr">
@@ -26966,17 +26966,17 @@
       </c>
       <c r="K76" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Region: cross-regional / ABNJ; issue: EU-facing technology standards / regulatory alignment</t>
+          <t xml:space="preserve">Region: cross-regional / ABNJ; issue: Critical raw materials × R&amp;I / technology</t>
         </is>
       </c>
       <c r="L76" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Detecting and responding to cybersecurity incidents - Publications Office of the EU. Cybersecurity is also a key element.</t>
+          <t xml:space="preserve">JRC assesses 74 substitution, design, process, packaging and circularity options across five critical-material portfolios.</t>
         </is>
       </c>
       <c r="M76" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Deployment bottlenecks identify where European R&amp;I capacity and infrastructure are needed.</t>
         </is>
       </c>
       <c r="N76" s="3" t="inlineStr">
@@ -27001,12 +27001,12 @@
       </c>
       <c r="R76" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">EU Publications Office</t>
+          <t xml:space="preserve">COELHO, Fernando, OLIVEIRA, Filipa M., MOURDIKOUDIS, Stefanos, PENNINGTON, David</t>
         </is>
       </c>
       <c r="S76" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://op.europa.eu/o/opportal-service/download-handler?identifier=692a9852-b703-11f1-81de-01aa75ed71a1&amp;format=pdf&amp;language=en&amp;productionSystem=cellar&amp;part=</t>
+          <t xml:space="preserve">https://publications.jrc.ec.europa.eu/repository/handle/JRC147525?mode=full</t>
         </is>
       </c>
     </row>
@@ -27016,27 +27016,27 @@
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Allow dual-use research in next Horizon Europe, research ministers urge MEPs</t>
+          <t xml:space="preserve">Detecting and responding to cybersecurity incidents - Publications Office of the EU</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-28T21:34Z</t>
+          <t xml:space="preserve">2026-09-22</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Science|Business</t>
+          <t xml:space="preserve">EU Publications Office</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Main C</t>
+          <t xml:space="preserve">Main A</t>
         </is>
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">C</t>
+          <t xml:space="preserve">A</t>
         </is>
       </c>
       <c r="G77" s="3" t="inlineStr">
@@ -27051,7 +27051,7 @@
       </c>
       <c r="I77" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Research security / dual use</t>
+          <t xml:space="preserve">EU-facing technology standards / regulatory alignment</t>
         </is>
       </c>
       <c r="J77" s="3" t="inlineStr">
@@ -27061,17 +27061,17 @@
       </c>
       <c r="K77" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Region: cross-regional / ABNJ; issue: Research security / dual use</t>
+          <t xml:space="preserve">Region: cross-regional / ABNJ; issue: EU-facing technology standards / regulatory alignment</t>
         </is>
       </c>
       <c r="L77" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ministers from several European countries urged Parliament to support dual-use research in the next Horizon Europe.</t>
+          <t xml:space="preserve">Detecting and responding to cybersecurity incidents - Publications Office of the EU. Cybersecurity is also a key element.</t>
         </is>
       </c>
       <c r="M77" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Their joint intervention affects live negotiations over the scope of EU research funding.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="N77" s="3" t="inlineStr">
@@ -27096,12 +27096,12 @@
       </c>
       <c r="R77" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">EU Publications Office</t>
         </is>
       </c>
       <c r="S77" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://news.google.com/rss/articles/CBMizAFBVV95cUxPMkhkTkprc0VSQUplbmhoOWx5UzJxQnYxQ0JqRXhaYlBrOWRqY2YwZnQ2cnlKTmpYcG9jZXB2MVVjSkIwTlYtRVc4ZTdoVkVDcGhKSmZCaVE0dk1NaWNvQjZDV19oTnNZbHpKMG5RMVRqV0ctR0dXSmFaR3oxaUZNcEotYU1fNGctUWZobl85aDVHd0dPUXpjZmRiUkpoWDBhZ1QwVzFMaWtJdkNFUmpFT3FZdFVic3lKWUdkVWhfRlNMVVFlQmxab1RmQ2w?oc=5</t>
+          <t xml:space="preserve">https://op.europa.eu/o/opportal-service/download-handler?identifier=692a9852-b703-11f1-81de-01aa75ed71a1&amp;format=pdf&amp;language=en&amp;productionSystem=cellar&amp;part=</t>
         </is>
       </c>
     </row>
@@ -27111,27 +27111,27 @@
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reducing dependencies on Critical Raw Materials with advanced materials</t>
+          <t xml:space="preserve">Allow dual-use research in next Horizon Europe, research ministers urge MEPs</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-30</t>
+          <t xml:space="preserve">2026-09-28T21:34Z</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">JRC Publications Repository</t>
+          <t xml:space="preserve">Science|Business</t>
         </is>
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Main A</t>
+          <t xml:space="preserve">Main C</t>
         </is>
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">C</t>
         </is>
       </c>
       <c r="G78" s="3" t="inlineStr">
@@ -27146,7 +27146,7 @@
       </c>
       <c r="I78" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Critical raw materials × R&amp;I / technology</t>
+          <t xml:space="preserve">Research security / dual use</t>
         </is>
       </c>
       <c r="J78" s="3" t="inlineStr">
@@ -27156,17 +27156,17 @@
       </c>
       <c r="K78" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Region: cross-regional / ABNJ; issue: Critical raw materials × R&amp;I / technology</t>
+          <t xml:space="preserve">Region: cross-regional / ABNJ; issue: Research security / dual use</t>
         </is>
       </c>
       <c r="L78" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">JRC identifies advanced-material substitution, efficiency and circularity as ways to reduce EU critical-material dependencies.</t>
+          <t xml:space="preserve">Ministers from several European countries urged Parliament to support dual-use research in the next Horizon Europe.</t>
         </is>
       </c>
       <c r="M78" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">It maps research and innovation needs tied directly to EU supply security and competitiveness.</t>
+          <t xml:space="preserve">Their joint intervention affects live negotiations over the scope of EU research funding.</t>
         </is>
       </c>
       <c r="N78" s="3" t="inlineStr">
@@ -27191,12 +27191,12 @@
       </c>
       <c r="R78" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">COELHO, Fernando, PENNINGTON, David, SALA, Serenella</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="S78" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://publications.jrc.ec.europa.eu/repository/handle/JRC148453</t>
+          <t xml:space="preserve">https://news.google.com/rss/articles/CBMizAFBVV95cUxPMkhkTkprc0VSQUplbmhoOWx5UzJxQnYxQ0JqRXhaYlBrOWRqY2YwZnQ2cnlKTmpYcG9jZXB2MVVjSkIwTlYtRVc4ZTdoVkVDcGhKSmZCaVE0dk1NaWNvQjZDV19oTnNZbHpKMG5RMVRqV0ctR0dXSmFaR3oxaUZNcEotYU1fNGctUWZobl85aDVHd0dPUXpjZmRiUkpoWDBhZ1QwVzFMaWtJdkNFUmpFT3FZdFVic3lKWUdkVWhfRlNMVVFlQmxab1RmQ2w?oc=5</t>
         </is>
       </c>
     </row>
@@ -27206,27 +27206,27 @@
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Europe’s carmakers compete with AI for chips and critical materials</t>
+          <t xml:space="preserve">Reducing dependencies on Critical Raw Materials with advanced materials</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-30T10:39Z</t>
+          <t xml:space="preserve">2026-09-30</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Euronews</t>
+          <t xml:space="preserve">JRC Publications Repository</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Main C</t>
+          <t xml:space="preserve">Main A</t>
         </is>
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">C</t>
+          <t xml:space="preserve">A</t>
         </is>
       </c>
       <c r="G79" s="3" t="inlineStr">
@@ -27256,12 +27256,12 @@
       </c>
       <c r="L79" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">A new report says European carmakers increasingly compete with AI and data centres for chips and critical materials.</t>
+          <t xml:space="preserve">JRC identifies advanced-material substitution, efficiency and circularity as ways to reduce EU critical-material dependencies.</t>
         </is>
       </c>
       <c r="M79" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">The finding links European industrial technology capacity to constrained strategic inputs.</t>
+          <t xml:space="preserve">It maps research and innovation needs tied directly to EU supply security and competitiveness.</t>
         </is>
       </c>
       <c r="N79" s="3" t="inlineStr">
@@ -27286,12 +27286,12 @@
       </c>
       <c r="R79" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">COELHO, Fernando, PENNINGTON, David, SALA, Serenella</t>
         </is>
       </c>
       <c r="S79" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://news.google.com/rss/articles/CBMiqAFBVV95cUxQU1BaSVprUWJOWWxrZGM1R00xemZnOFlEMUVxSG15UUV4a3VzUWZOaFpiYk8xaFJKSUxpTXpXMy1lcmswbGdzYU1zVGxfMEt0eS1vUWV0TDdYeDNJNWhucXdxQlVPbzdMamJmOFBNcVZzanJoNVhRVVU1T2JHbWI1MXNaYy1RT3VSNy1yNDVtWGxyQkcwTkpLWVFDNzQwcUZYUXMxRnZfMjI?oc=5</t>
+          <t xml:space="preserve">https://publications.jrc.ec.europa.eu/repository/handle/JRC148453</t>
         </is>
       </c>
     </row>
@@ -27301,27 +27301,27 @@
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">R&amp;I needs to reduce critical raw materials through advanced materials in construction</t>
+          <t xml:space="preserve">Europe’s carmakers compete with AI for chips and critical materials</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-01</t>
+          <t xml:space="preserve">2026-09-30T10:39Z</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">JRC Publications Repository</t>
+          <t xml:space="preserve">Euronews</t>
         </is>
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Main A</t>
+          <t xml:space="preserve">Main C</t>
         </is>
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">C</t>
         </is>
       </c>
       <c r="G80" s="3" t="inlineStr">
@@ -27351,12 +27351,12 @@
       </c>
       <c r="L80" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">JRC compares 43 substitution, design, process and circularity routes for critical materials used in construction.</t>
+          <t xml:space="preserve">A new report says European carmakers increasingly compete with AI and data centres for chips and critical materials.</t>
         </is>
       </c>
       <c r="M80" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">The report identifies qualification, pilot-line and scale-up constraints for EU deployment.</t>
+          <t xml:space="preserve">The finding links European industrial technology capacity to constrained strategic inputs.</t>
         </is>
       </c>
       <c r="N80" s="3" t="inlineStr">
@@ -27381,12 +27381,12 @@
       </c>
       <c r="R80" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">HAVERIKU, Sara, LAMPERTI, TORNAGHI Marco</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="S80" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://publications.jrc.ec.europa.eu/repository/handle/JRC147428?mode=full</t>
+          <t xml:space="preserve">https://news.google.com/rss/articles/CBMiqAFBVV95cUxQU1BaSVprUWJOWWxrZGM1R00xemZnOFlEMUVxSG15UUV4a3VzUWZOaFpiYk8xaFJKSUxpTXpXMy1lcmswbGdzYU1zVGxfMEt0eS1vUWV0TDdYeDNJNWhucXdxQlVPbzdMamJmOFBNcVZzanJoNVhRVVU1T2JHbWI1MXNaYy1RT3VSNy1yNDVtWGxyQkcwTkpLWVFDNzQwcUZYUXMxRnZfMjI?oc=5</t>
         </is>
       </c>
     </row>
@@ -27396,27 +27396,27 @@
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dual-use restrictions risk holding back research, Nordic universities say</t>
+          <t xml:space="preserve">R&amp;I needs to reduce critical raw materials through advanced materials in construction</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-01T14:50Z</t>
+          <t xml:space="preserve">2026-10-01</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Science|Business</t>
+          <t xml:space="preserve">JRC Publications Repository</t>
         </is>
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Main C</t>
+          <t xml:space="preserve">Main A</t>
         </is>
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">C</t>
+          <t xml:space="preserve">A</t>
         </is>
       </c>
       <c r="G81" s="3" t="inlineStr">
@@ -27431,27 +27431,27 @@
       </c>
       <c r="I81" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Research security / dual use</t>
+          <t xml:space="preserve">Critical raw materials × R&amp;I / technology</t>
         </is>
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Universities / research institutions</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K81" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Region: cross-regional / ABNJ; issue: Research security / dual use</t>
+          <t xml:space="preserve">Region: cross-regional / ABNJ; issue: Critical raw materials × R&amp;I / technology</t>
         </is>
       </c>
       <c r="L81" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nordic university leaders warned that overly restrictive dual-use rules could exclude scientifically valuable Horizon Europe research.</t>
+          <t xml:space="preserve">JRC compares 43 substitution, design, process and circularity routes for critical materials used in construction.</t>
         </is>
       </c>
       <c r="M81" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Their intervention feeds an active EU decision over the scope of the next research programme.</t>
+          <t xml:space="preserve">The report identifies qualification, pilot-line and scale-up constraints for EU deployment.</t>
         </is>
       </c>
       <c r="N81" s="3" t="inlineStr">
@@ -27476,12 +27476,12 @@
       </c>
       <c r="R81" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">HAVERIKU, Sara, LAMPERTI, TORNAGHI Marco</t>
         </is>
       </c>
       <c r="S81" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://news.google.com/rss/articles/CBMivAFBVV95cUxPNl9UZUx6VWZ4bmlmeUg2a2xjUV9DdTBBaFJEM2o4emtxaHNHMnFvcnNicHdXZkxET0ZYMWkyckNXNVZtamZsREhuQUVYLVFrQ0dTT1pRb1M5N2F5LVhlVGU2cWlpcndxbDhjSV9tZThzRGlpWTBHY3FYdHU3NE1wOGpGNng3aUpBWVFXQU1sNVBlU05CeWJ2UGNjWGVIMng1dEtJWWY5M0ZtZnNHajNxcFZKdHRpRGYwb2F4Sg?oc=5</t>
+          <t xml:space="preserve">https://publications.jrc.ec.europa.eu/repository/handle/JRC147428?mode=full</t>
         </is>
       </c>
     </row>
@@ -27491,17 +27491,17 @@
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Horizon Europe launches a new research and innovation call on nature</t>
+          <t xml:space="preserve">Dual-use restrictions risk holding back research, Nordic universities say</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-02T08:13Z</t>
+          <t xml:space="preserve">2026-10-01T14:50Z</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">EU Research &amp; Innovation</t>
+          <t xml:space="preserve">Science|Business</t>
         </is>
       </c>
       <c r="E82" s="3" t="inlineStr">
@@ -27526,27 +27526,27 @@
       </c>
       <c r="I82" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">EU external R&amp;I partnerships / enlargement</t>
+          <t xml:space="preserve">Research security / dual use</t>
         </is>
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Universities / research institutions</t>
         </is>
       </c>
       <c r="K82" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Region: cross-regional / ABNJ; issue: EU external R&amp;I partnerships / enlargement</t>
+          <t xml:space="preserve">Region: cross-regional / ABNJ; issue: Research security / dual use</t>
         </is>
       </c>
       <c r="L82" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">The Commission announced a €230 million Horizon Europe nature call covering ten biodiversity research topics.</t>
+          <t xml:space="preserve">Nordic university leaders warned that overly restrictive dual-use rules could exclude scientifically valuable Horizon Europe research.</t>
         </is>
       </c>
       <c r="M82" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">The new call explicitly increases R&amp;I funding for European biodiversity, monitoring and ecosystem restoration.</t>
+          <t xml:space="preserve">Their intervention feeds an active EU decision over the scope of the next research programme.</t>
         </is>
       </c>
       <c r="N82" s="3" t="inlineStr">
@@ -27576,7 +27576,7 @@
       </c>
       <c r="S82" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://news.google.com/rss/articles/CBMi8gFBVV95cUxNVzJrbnB6clF0YzUzZmkxUUZ3V2hpV0xfN2lILXFyOGFoRExET1lvUzdKakhKR1NyS2pQdWVnSVhkWV9kM3U2NGtjaEhTeURmaXJNYmJqTDNzVUFiM0VDYnFhNW1pMmZlb3pHMkVqemkyNllRTW5OSDdPQjZwME1xODNzeHRjdDFuTF9qT0MtMWZwSWwxRC1UX25wRWxfLWUydDhITnVJcTYwQ1ptZ1JoX2lYdC0ta3l5NVBuYVN2Q1lwQndzUnZiSnJEbDhQenZVT3M4WUdvaWdmMlVQYlpwQ3N5X3NPTXNfRlhsc19DX0I5Zw?oc=5</t>
+          <t xml:space="preserve">https://news.google.com/rss/articles/CBMivAFBVV95cUxPNl9UZUx6VWZ4bmlmeUg2a2xjUV9DdTBBaFJEM2o4emtxaHNHMnFvcnNicHdXZkxET0ZYMWkyckNXNVZtamZsREhuQUVYLVFrQ0dTT1pRb1M5N2F5LVhlVGU2cWlpcndxbDhjSV9tZThzRGlpWTBHY3FYdHU3NE1wOGpGNng3aUpBWVFXQU1sNVBlU05CeWJ2UGNjWGVIMng1dEtJWWY5M0ZtZnNHajNxcFZKdHRpRGYwb2F4Sg?oc=5</t>
         </is>
       </c>
     </row>
@@ -27586,17 +27586,17 @@
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">EU weighs mirroring Donald Trump in securing critical minerals</t>
+          <t xml:space="preserve">Horizon Europe launches a new research and innovation call on nature</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-26T05:00Z</t>
+          <t xml:space="preserve">2026-10-02T08:13Z</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Financial Times</t>
+          <t xml:space="preserve">EU Research &amp; Innovation</t>
         </is>
       </c>
       <c r="E83" s="3" t="inlineStr">
@@ -27621,7 +27621,7 @@
       </c>
       <c r="I83" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Critical raw materials × R&amp;I / technology</t>
+          <t xml:space="preserve">EU external R&amp;I partnerships / enlargement</t>
         </is>
       </c>
       <c r="J83" s="3" t="inlineStr">
@@ -27631,17 +27631,17 @@
       </c>
       <c r="K83" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Region: cross-regional / ABNJ; issue: Critical raw materials × R&amp;I / technology</t>
+          <t xml:space="preserve">Region: cross-regional / ABNJ; issue: EU external R&amp;I partnerships / enlargement</t>
         </is>
       </c>
       <c r="L83" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">European lawmakers backed a proposed Critical Raw Materials Centre able to acquire stakes in mineral projects and coordinate stockpiles.</t>
+          <t xml:space="preserve">The Commission announced a €230 million Horizon Europe nature call covering ten biodiversity research topics.</t>
         </is>
       </c>
       <c r="M83" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Proposed investment and stockpiling instruments would address strategic material inputs for European clean technology, batteries and defence innovation.</t>
+          <t xml:space="preserve">The new call explicitly increases R&amp;I funding for European biodiversity, monitoring and ecosystem restoration.</t>
         </is>
       </c>
       <c r="N83" s="3" t="inlineStr">
@@ -27671,27 +27671,27 @@
       </c>
       <c r="S83" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://news.google.com/rss/articles/CBMihAFBVV95cUxPTkh2ek1Gc3lfdzhmdi1xc25PbEt1UHVLMjdXeHN1V1BuLTR3RHhLVDhhWFAxZXdCM3ZrYXA1c05CX1hrTkZabEt2eGUxSGRfQXRZWGdCTFNIZl9iMnVNT3c4UTFoMTZyZmRoTlMxZHJRSzFRSlo4dzV4UkhPRHNtekZGS3I?oc=5</t>
+          <t xml:space="preserve">https://news.google.com/rss/articles/CBMi8gFBVV95cUxNVzJrbnB6clF0YzUzZmkxUUZ3V2hpV0xfN2lILXFyOGFoRExET1lvUzdKakhKR1NyS2pQdWVnSVhkWV9kM3U2NGtjaEhTeURmaXJNYmJqTDNzVUFiM0VDYnFhNW1pMmZlb3pHMkVqemkyNllRTW5OSDdPQjZwME1xODNzeHRjdDFuTF9qT0MtMWZwSWwxRC1UX25wRWxfLWUydDhITnVJcTYwQ1ptZ1JoX2lYdC0ta3l5NVBuYVN2Q1lwQndzUnZiSnJEbDhQenZVT3M4WUdvaWdmMlVQYlpwQ3N5X3NPTXNfRlhsc19DX0I5Zw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">EU-China trade and investment relations</t>
+          <t xml:space="preserve">EU weighs mirroring Donald Trump in securing critical minerals</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-28T16:04Z</t>
+          <t xml:space="preserve">2026-10-26T05:00Z</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">European Parliament</t>
+          <t xml:space="preserve">Financial Times</t>
         </is>
       </c>
       <c r="E84" s="3" t="inlineStr">
@@ -27706,17 +27706,17 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">China</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H84" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asia &amp; Pacific</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I84" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transnational R&amp;I and innovation policy</t>
+          <t xml:space="preserve">Critical raw materials × R&amp;I / technology</t>
         </is>
       </c>
       <c r="J84" s="3" t="inlineStr">
@@ -27726,17 +27726,17 @@
       </c>
       <c r="K84" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Region: China; issue: Transnational R&amp;I and innovation policy</t>
+          <t xml:space="preserve">Region: cross-regional / ABNJ; issue: Critical raw materials × R&amp;I / technology</t>
         </is>
       </c>
       <c r="L84" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">EU-China trade and investment relations. The repository record provides substantive source material sufficient for a terminal Deep Scan.</t>
+          <t xml:space="preserve">European lawmakers backed a proposed Critical Raw Materials Centre able to acquire stakes in mineral projects and coordinate stockpiles.</t>
         </is>
       </c>
       <c r="M84" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Proposed investment and stockpiling instruments would address strategic material inputs for European clean technology, batteries and defence innovation.</t>
         </is>
       </c>
       <c r="N84" s="3" t="inlineStr">
@@ -27766,7 +27766,7 @@
       </c>
       <c r="S84" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://news.google.com/rss/articles/CBMifkFVX3lxTE5na2d5djZmZnloSXVwUGVEeTRhOE9rLVFUSUE0VXBlaGUyZUFNdk5wSm9JMEZ1VDd6Yk5CakJDdV9wdjhQYi1FNFd5VkhITWpPMlo0YkdJUkd4Ti1ueUJXdVhDam1yUEZTMnhIcmRQWm4tTE80MzlRNUhiUGlSdw?oc=5</t>
+          <t xml:space="preserve">https://news.google.com/rss/articles/CBMihAFBVV95cUxPTkh2ek1Gc3lfdzhmdi1xc25PbEt1UHVLMjdXeHN1V1BuLTR3RHhLVDhhWFAxZXdCM3ZrYXA1c05CX1hrTkZabEt2eGUxSGRfQXRZWGdCTFNIZl9iMnVNT3c4UTFoMTZyZmRoTlMxZHJRSzFRSlo4dzV4UkhPRHNtekZGS3I?oc=5</t>
         </is>
       </c>
     </row>
@@ -27776,97 +27776,192 @@
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">EU-China trade and investment relations</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-28T16:04Z</t>
+        </is>
+      </c>
+      <c r="D85" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">European Parliament</t>
+        </is>
+      </c>
+      <c r="E85" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Main C</t>
+        </is>
+      </c>
+      <c r="F85" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C</t>
+        </is>
+      </c>
+      <c r="G85" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">China</t>
+        </is>
+      </c>
+      <c r="H85" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Asia &amp; Pacific</t>
+        </is>
+      </c>
+      <c r="I85" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Transnational R&amp;I and innovation policy</t>
+        </is>
+      </c>
+      <c r="J85" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K85" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Region: China; issue: Transnational R&amp;I and innovation policy</t>
+        </is>
+      </c>
+      <c r="L85" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EU-China trade and investment relations. The repository record provides substantive source material sufficient for a terminal Deep Scan.</t>
+        </is>
+      </c>
+      <c r="M85" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N85" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">keep</t>
+        </is>
+      </c>
+      <c r="O85" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Review / awaiting authoritative retention</t>
+        </is>
+      </c>
+      <c r="P85" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Q85" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R85" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S85" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://news.google.com/rss/articles/CBMifkFVX3lxTE5na2d5djZmZnloSXVwUGVEeTRhOE9rLVFUSUE0VXBlaGUyZUFNdk5wSm9JMEZ1VDd6Yk5CakJDdV9wdjhQYi1FNFd5VkhITWpPMlo0YkdJUkd4Ti1ueUJXdVhDam1yUEZTMnhIcmRQWm4tTE80MzlRNUhiUGlSdw?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="3">
+        <v>58</v>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">EU-China political relations | 05-10-2026 | News</t>
         </is>
       </c>
-      <c r="C85" s="3" t="inlineStr">
+      <c r="C86" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-10-01T13:52Z</t>
         </is>
       </c>
-      <c r="D85" s="3" t="inlineStr">
+      <c r="D86" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">European Parliament</t>
         </is>
       </c>
-      <c r="E85" s="3" t="inlineStr">
+      <c r="E86" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Main C</t>
         </is>
       </c>
-      <c r="F85" s="3" t="inlineStr">
+      <c r="F86" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">C</t>
         </is>
       </c>
-      <c r="G85" s="3" t="inlineStr">
+      <c r="G86" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">China</t>
         </is>
       </c>
-      <c r="H85" s="3" t="inlineStr">
+      <c r="H86" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Asia &amp; Pacific</t>
         </is>
       </c>
-      <c r="I85" s="3" t="inlineStr">
+      <c r="I86" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Transnational R&amp;I and innovation policy</t>
         </is>
       </c>
-      <c r="J85" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="K85" s="3" t="inlineStr">
+      <c r="J86" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K86" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Region: China; issue: Transnational R&amp;I and innovation policy</t>
         </is>
       </c>
-      <c r="L85" s="3" t="inlineStr">
+      <c r="L86" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">EU-China political relations | 05-10-2026 | News.</t>
         </is>
       </c>
-      <c r="M85" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N85" s="3" t="inlineStr">
+      <c r="M86" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N86" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">keep</t>
         </is>
       </c>
-      <c r="O85" s="3" t="inlineStr">
+      <c r="O86" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Review / awaiting authoritative retention</t>
         </is>
       </c>
-      <c r="P85" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="Q85" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="R85" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="S85" s="3" t="inlineStr">
+      <c r="P86" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Q86" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R86" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S86" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">https://news.google.com/rss/articles/CBMiogFBVV95cUxQWmlaa2hLZEw1UjBQMG9tTzMxWC1BMzBJRnkwTmhuajBMSHNrSUdYTWh4bXd5N0lVWlhhMTNHLUNRaS1id1JYZU1PUVljMnU5X2ZBc0VtN2g1TUtFeUU4dEhzTGYtdG5OeGFFeTZIb3lhVGREN3BjWElOZ0s0SnBVOFJqVkl5anVYV0tYdzVjS1pYSm9BX3hUUVN4WWdRX05WMXc?oc=5</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S85"/>
+  <autoFilter ref="A1:S86"/>
 </worksheet>
 </file>
 
@@ -28888,7 +28983,7 @@
         <v>138</v>
       </c>
       <c r="D56" s="3">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="57">
@@ -28924,7 +29019,7 @@
         <v>2</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -29061,7 +29156,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-31T02:22:57+00:00</t>
+          <t xml:space="preserve">2026-10-31T06:24:03+00:00</t>
         </is>
       </c>
     </row>
@@ -29082,7 +29177,7 @@
         </is>
       </c>
       <c r="B5" s="3">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6">

--- a/Relevance Stuff/relevance_stuff.xlsx
+++ b/Relevance Stuff/relevance_stuff.xlsx
@@ -29156,7 +29156,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-31T06:24:03+00:00</t>
+          <t xml:space="preserve">2026-10-31T08:50:45+00:00</t>
         </is>
       </c>
     </row>

--- a/Relevance Stuff/relevance_stuff.xlsx
+++ b/Relevance Stuff/relevance_stuff.xlsx
@@ -29156,7 +29156,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-31T08:50:45+00:00</t>
+          <t xml:space="preserve">2026-10-31T09:27:05+00:00</t>
         </is>
       </c>
     </row>

--- a/Relevance Stuff/relevance_stuff.xlsx
+++ b/Relevance Stuff/relevance_stuff.xlsx
@@ -52029,7 +52029,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-31T11:31:33+00:00</t>
+          <t xml:space="preserve">2026-10-31T12:34:14+00:00</t>
         </is>
       </c>
     </row>
@@ -52222,7 +52222,7 @@
         </is>
       </c>
       <c r="B6" s="3">
-        <v>3622</v>
+        <v>3623</v>
       </c>
     </row>
     <row r="7">
@@ -52294,7 +52294,7 @@
         </is>
       </c>
       <c r="B13" s="3">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="14">
@@ -52304,7 +52304,7 @@
         </is>
       </c>
       <c r="B14" s="3">
-        <v>765</v>
+        <v>766</v>
       </c>
     </row>
     <row r="15">
@@ -52364,7 +52364,7 @@
         </is>
       </c>
       <c r="B20" s="3">
-        <v>4867</v>
+        <v>4869</v>
       </c>
     </row>
     <row r="21">
@@ -52504,7 +52504,7 @@
         </is>
       </c>
       <c r="B34" s="3">
-        <v>3622</v>
+        <v>3623</v>
       </c>
     </row>
     <row r="35">

--- a/Relevance Stuff/relevance_stuff.xlsx
+++ b/Relevance Stuff/relevance_stuff.xlsx
@@ -48833,7 +48833,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-31T11:45:06+00:00</t>
+          <t xml:space="preserve">2026-10-31T13:19:01+00:00</t>
         </is>
       </c>
     </row>
@@ -49070,7 +49070,7 @@
         </is>
       </c>
       <c r="B7" s="3">
-        <v>3622</v>
+        <v>3623</v>
       </c>
     </row>
     <row r="8">
@@ -49142,7 +49142,7 @@
         </is>
       </c>
       <c r="B14" s="3">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="15">
@@ -49152,7 +49152,7 @@
         </is>
       </c>
       <c r="B15" s="3">
-        <v>765</v>
+        <v>766</v>
       </c>
     </row>
     <row r="16">
@@ -49212,7 +49212,7 @@
         </is>
       </c>
       <c r="B21" s="3">
-        <v>4558</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="22">
@@ -49352,7 +49352,7 @@
         </is>
       </c>
       <c r="B35" s="3">
-        <v>3622</v>
+        <v>3623</v>
       </c>
     </row>
     <row r="36">

--- a/Relevance Stuff/relevance_stuff.xlsx
+++ b/Relevance Stuff/relevance_stuff.xlsx
@@ -46463,46 +46463,46 @@
     </row>
     <row r="3">
       <c r="A3" s="3">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">EU-China research cooperation limited to ‘targeted areas’</t>
+          <t xml:space="preserve">The European Regulatory Mirage: Epistemic Dependence and the Limits of AI Governance</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-10T07:00Z</t>
+          <t xml:space="preserve">2026-10-30</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Research Professional News</t>
+          <t xml:space="preserve">JCMS Journal of Common Market Studies</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Main C — active</t>
+          <t xml:space="preserve">Main A — active</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">C — active</t>
+          <t xml:space="preserve">A</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">China</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asia &amp; Pacific</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transnational R&amp;I and innovation policy</t>
+          <t xml:space="preserve">EU external R&amp;I partnerships / enlargement; EU-facing technology standards / regulatory alignment</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -46512,7 +46512,7 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Region: China; issue: Transnational R&amp;I and innovation policy</t>
+          <t xml:space="preserve">Region: cross-regional / ABNJ; issue: EU external R&amp;I partnerships / enlargement, EU-facing technology standards / regulatory alignment</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -46522,7 +46522,7 @@
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">This may shift the risk–reward balance of EU–China research, technology and innovation cooperation.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
@@ -46552,57 +46552,57 @@
       </c>
       <c r="S3" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Carlos García-Llorente, José Ignacio Olmeda Martos</t>
         </is>
       </c>
       <c r="T3" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://news.google.com/rss/articles/CBMixwFBVV95cUxQR1JiOFNtQlZBYUJUUThOYXVYSjFad2h0TG5OSm9ZdDBaY0NrbVk3UkkxUlZJMWFPczJySWd5RmwtYmZsdFE2bS1iOGJnMHFacHBtWE5GUWpqRTN3QXR4SHVtdE1ZRktGY3V6SUc0OWtIQVhSMUp5QVk2ZjE0N29TdFp6ZzgwTmx0aXpkMFpsM2lfb2xrWUtyWXJLY1hlYnRqNEhQWHNZLUhZZThpeklQU3NHWXQ2SGZhNkpmTllLU1JCN1NMU2Jv?oc=5</t>
+          <t xml:space="preserve">https://doi.org/10.1111/jcms.70181</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Securing the Future of Open Data in the United States: Introducing the OPEN Government Data Act</t>
+          <t xml:space="preserve">EU-China research cooperation limited to ‘targeted areas’</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2016-01-01</t>
+          <t xml:space="preserve">2026-08-10T07:00Z</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Information Technology and Innovation Foundation</t>
+          <t xml:space="preserve">Research Professional News</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Historical</t>
+          <t xml:space="preserve">Main C — active</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">C — active</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">United States</t>
+          <t xml:space="preserve">China</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Americas</t>
+          <t xml:space="preserve">Asia &amp; Pacific</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Country / regional R&amp;I policy or strategic foresight</t>
+          <t xml:space="preserve">Transnational R&amp;I and innovation policy</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -46612,22 +46612,22 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Region: United States; issue: Country / regional R&amp;I policy or strategic foresight</t>
+          <t xml:space="preserve">Region: China; issue: Transnational R&amp;I and innovation policy</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reports, articles, commentary, analysis, and events covering the intersection of technological innovation and public policy, including: economic issues related to innovation, productivity, and competitiveness; technology issues in the areas of information technology and data, broadband telecommunications, advanced manufacturing…</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">This bears on Europe's research and innovation position. It is useful history for judging which earlier pressures still matter now.</t>
+          <t xml:space="preserve">This may shift the risk–reward balance of EU–China research, technology and innovation cooperation.</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">not yet checked</t>
+          <t xml:space="preserve">provisional</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
@@ -46657,7 +46657,7 @@
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://itif.org/media/securing-future-open-data-united-states-introducing-open-government-data-act/</t>
+          <t xml:space="preserve">https://news.google.com/rss/articles/CBMixwFBVV95cUxQR1JiOFNtQlZBYUJUUThOYXVYSjFad2h0TG5OSm9ZdDBaY0NrbVk3UkkxUlZJMWFPczJySWd5RmwtYmZsdFE2bS1iOGJnMHFacHBtWE5GUWpqRTN3QXR4SHVtdE1ZRktGY3V6SUc0OWtIQVhSMUp5QVk2ZjE0N29TdFp6ZzgwTmx0aXpkMFpsM2lfb2xrWUtyWXJLY1hlYnRqNEhQWHNZLUhZZThpeklQU3NHWXQ2SGZhNkpmTllLU1JCN1NMU2Jv?oc=5</t>
         </is>
       </c>
     </row>
@@ -46667,17 +46667,17 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">China’s Overlooked AI Strategy | Center for Security and Emerging Technology</t>
+          <t xml:space="preserve">Securing the Future of Open Data in the United States: Introducing the OPEN Government Data Act</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-07-25</t>
+          <t xml:space="preserve">2016-01-01</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CSET</t>
+          <t xml:space="preserve">Information Technology and Innovation Foundation</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -46692,12 +46692,12 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">China</t>
+          <t xml:space="preserve">United States</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asia &amp; Pacific</t>
+          <t xml:space="preserve">Americas</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -46707,17 +46707,17 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Foreign-affairs / trade / non-research ministries</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Region: China; issue: Country / regional R&amp;I policy or strategic foresight</t>
+          <t xml:space="preserve">Region: United States; issue: Country / regional R&amp;I policy or strategic foresight</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">The place to find CSET's publications, reports, and people In The News China’s Overlooked AI Strategy Foreign Affairs July 25, 2025 Owen J.</t>
+          <t xml:space="preserve">Reports, articles, commentary, analysis, and events covering the intersection of technological innovation and public policy, including: economic issues related to innovation, productivity, and competitiveness; technology issues in the areas of information technology and data, broadband telecommunications, advanced manufacturing…</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
@@ -46757,7 +46757,7 @@
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://cset.georgetown.edu/article/chinas-overlooked-ai-strategy/</t>
+          <t xml:space="preserve">https://itif.org/media/securing-future-open-data-united-states-introducing-open-government-data-act/</t>
         </is>
       </c>
     </row>
@@ -46767,17 +46767,17 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pursuing practicality and autonomy in the Indo-Pacific: the case of ROK-India Special Strategic Partnership</t>
+          <t xml:space="preserve">China’s Overlooked AI Strategy | Center for Security and Emerging Technology</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-15</t>
+          <t xml:space="preserve">2025-07-25</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asia Europe Journal</t>
+          <t xml:space="preserve">CSET</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -46792,7 +46792,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">India</t>
+          <t xml:space="preserve">China</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
@@ -46807,17 +46807,17 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Foreign-affairs / trade / non-research ministries</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Region: India; issue: Country / regional R&amp;I policy or strategic foresight</t>
+          <t xml:space="preserve">Region: China; issue: Country / regional R&amp;I policy or strategic foresight</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">The Indo-Pacific theater is emerging as a region that calls for complex geostrategic calculations.</t>
+          <t xml:space="preserve">The place to find CSET's publications, reports, and people In The News China’s Overlooked AI Strategy Foreign Affairs July 25, 2025 Owen J.</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
@@ -46852,32 +46852,32 @@
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hyun Ji Rim</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://doi.org/10.1007/s10308-025-00768-7</t>
+          <t xml:space="preserve">https://cset.georgetown.edu/article/chinas-overlooked-ai-strategy/</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ASEAN’s flagship universities and regional integration initiatives</t>
+          <t xml:space="preserve">Pursuing practicality and autonomy in the Indo-Pacific: the case of ROK-India Special Strategic Partnership</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2017-12-04</t>
+          <t xml:space="preserve">2025-12-15</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Higher Education</t>
+          <t xml:space="preserve">Asia Europe Journal</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -46892,7 +46892,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ASEAN</t>
+          <t xml:space="preserve">India</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
@@ -46902,27 +46902,27 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transnational R&amp;I and innovation policy</t>
+          <t xml:space="preserve">Country / regional R&amp;I policy or strategic foresight</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Universities / research institutions</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Region: ASEAN; issue: Transnational R&amp;I and innovation policy</t>
+          <t xml:space="preserve">Region: India; issue: Country / regional R&amp;I policy or strategic foresight</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Purpose The purpose of this paper is to examine the role of Association of Southeast Asian Nations’ (ASEAN) flagship universities in moving the agenda of regional integration forward through academic/research collaboration and cooperation.</t>
+          <t xml:space="preserve">The Indo-Pacific theater is emerging as a region that calls for complex geostrategic calculations.</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">This bears on Europe's research workforce, skills and know-how. It is useful history for judging whether later policy really built durable European strength.</t>
+          <t xml:space="preserve">This bears on Europe's research and innovation position. It is useful history for judging which earlier pressures still matter now.</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
@@ -46952,12 +46952,12 @@
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Morshidi Sirat</t>
+          <t xml:space="preserve">Hyun Ji Rim</t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://doi.org/10.1108/heed-07-2017-0004</t>
+          <t xml:space="preserve">https://doi.org/10.1007/s10308-025-00768-7</t>
         </is>
       </c>
     </row>
@@ -46967,17 +46967,17 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">The data quagmire for German carmakers in China</t>
+          <t xml:space="preserve">ASEAN’s flagship universities and regional integration initiatives</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-05-06</t>
+          <t xml:space="preserve">2017-12-04</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">MERICS</t>
+          <t xml:space="preserve">Higher Education</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -46992,7 +46992,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">China</t>
+          <t xml:space="preserve">ASEAN</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
@@ -47002,27 +47002,27 @@
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Country / regional R&amp;I policy or strategic foresight</t>
+          <t xml:space="preserve">Transnational R&amp;I and innovation policy</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business / industry</t>
+          <t xml:space="preserve">Universities / research institutions</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Region: China; issue: Country / regional R&amp;I policy or strategic foresight</t>
+          <t xml:space="preserve">Region: ASEAN; issue: Transnational R&amp;I and innovation policy</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">The renewal of the Sino-German MoU on autonomous vehicles opens up questions around data privacy, security, and Germany’s industrial competitiveness, says Rebecca Arcesati.</t>
+          <t xml:space="preserve">Purpose The purpose of this paper is to examine the role of Association of Southeast Asian Nations’ (ASEAN) flagship universities in moving the agenda of regional integration forward through academic/research collaboration and cooperation.</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">This bears on Europe's ability to turn research into firms, production and scale. It is useful history for judging where European gains still depended on outside capital, technology, markets or access.</t>
+          <t xml:space="preserve">This bears on Europe's research workforce, skills and know-how. It is useful history for judging whether later policy really built durable European strength.</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
@@ -47052,12 +47052,12 @@
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Morshidi Sirat</t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://merics.org/en/comment/data-quagmire-german-carmakers-china</t>
+          <t xml:space="preserve">https://doi.org/10.1108/heed-07-2017-0004</t>
         </is>
       </c>
     </row>
@@ -47067,37 +47067,37 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">EU can compete with US AI giants, says Brussels’ frontier-model champion</t>
+          <t xml:space="preserve">The data quagmire for German carmakers in China</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-29T06:00Z</t>
+          <t xml:space="preserve">2024-05-06</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Financial Times</t>
+          <t xml:space="preserve">MERICS</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Main C — active</t>
+          <t xml:space="preserve">Historical</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">C — active</t>
+          <t xml:space="preserve">A</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">United States</t>
+          <t xml:space="preserve">China</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Americas</t>
+          <t xml:space="preserve">Asia &amp; Pacific</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
@@ -47107,27 +47107,27 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Business / industry</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Region: United States; issue: Country / regional R&amp;I policy or strategic foresight</t>
+          <t xml:space="preserve">Region: China; issue: Country / regional R&amp;I policy or strategic foresight</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">The renewal of the Sino-German MoU on autonomous vehicles opens up questions around data privacy, security, and Germany’s industrial competitiveness, says Rebecca Arcesati.</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">This may affect European access, investment or capability-building in a technology that is becoming strategically important.</t>
+          <t xml:space="preserve">This bears on Europe's ability to turn research into firms, production and scale. It is useful history for judging where European gains still depended on outside capital, technology, markets or access.</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">provisional</t>
+          <t xml:space="preserve">not yet checked</t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
@@ -47157,7 +47157,7 @@
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://news.google.com/rss/articles/CBMihAFBVV95cUxNNE0tYWZuVElPc1pqVXdBNjFpX3AwcDM4SEpWangyang0ZlZsb21TR0EtVzAyZlBaNk9mVzRqdEgyMXRaS3Brd1ZIZnpvTHJONEd6dXBiWm1LakY3eXMzN3hXZ0szQ0w4UDZBTmFjTmc4UV9xWjlqMUFHZTdoSGZwSE5GVHk?oc=5</t>
+          <t xml:space="preserve">https://merics.org/en/comment/data-quagmire-german-carmakers-china</t>
         </is>
       </c>
     </row>
@@ -47167,17 +47167,17 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">How Africa-Europe research is changing global health</t>
+          <t xml:space="preserve">EU can compete with US AI giants, says Brussels’ frontier-model champion</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-29T12:28Z</t>
+          <t xml:space="preserve">2026-10-29T06:00Z</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Science|Business</t>
+          <t xml:space="preserve">Financial Times</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -47192,12 +47192,12 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Africa (region)</t>
+          <t xml:space="preserve">United States</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Africa</t>
+          <t xml:space="preserve">Americas</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
@@ -47212,7 +47212,7 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Region: Africa (region); issue: Country / regional R&amp;I policy or strategic foresight</t>
+          <t xml:space="preserve">Region: United States; issue: Country / regional R&amp;I policy or strategic foresight</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
@@ -47222,7 +47222,7 @@
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">This may change Europe's relative research and innovation capacity in technologies that increasingly shape geopolitical power.</t>
+          <t xml:space="preserve">This may affect European access, investment or capability-building in a technology that is becoming strategically important.</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
@@ -47257,7 +47257,7 @@
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://news.google.com/rss/articles/CBMiigFBVV95cUxPZjRtYTlLZU4tRTU0S0VJdkZZZmZIR29PSFdzQUJPdWJnTGVNY2lmdHpRaUVqQzdrTFF2U0xpXzZZb0JLdDNUNkdUQllCZnJXX0tiLVc1VWJHd1lEMXpadHlXZGRWTTdDdGw1eWZmM3RUZjItV1BRbUNIZTJsdWRiZ0RUY25JODA4SWc?oc=5</t>
+          <t xml:space="preserve">https://news.google.com/rss/articles/CBMihAFBVV95cUxNNE0tYWZuVElPc1pqVXdBNjFpX3AwcDM4SEpWangyang0ZlZsb21TR0EtVzAyZlBaNk9mVzRqdEgyMXRaS3Brd1ZIZnpvTHJONEd6dXBiWm1LakY3eXMzN3hXZ0szQ0w4UDZBTmFjTmc4UV9xWjlqMUFHZTdoSGZwSE5GVHk?oc=5</t>
         </is>
       </c>
     </row>
@@ -47267,102 +47267,202 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">How Africa-Europe research is changing global health</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-29T12:28Z</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Science|Business</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Main C — active</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C — active</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Africa (region)</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Africa</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Country / regional R&amp;I policy or strategic foresight</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Region: Africa (region); issue: Country / regional R&amp;I policy or strategic foresight</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">This may change Europe's relative research and innovation capacity in technologies that increasingly shape geopolitical power.</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">provisional</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Deep Scan not complete</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not verified + retained</t>
+        </is>
+      </c>
+      <c r="Q11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://news.google.com/rss/articles/CBMiigFBVV95cUxPZjRtYTlLZU4tRTU0S0VJdkZZZmZIR29PSFdzQUJPdWJnTGVNY2lmdHpRaUVqQzdrTFF2U0xpXzZZb0JLdDNUNkdUQllCZnJXX0tiLVc1VWJHd1lEMXpadHlXZGRWTTdDdGw1eWZmM3RUZjItV1BRbUNIZTJsdWRiZ0RUY25JODA4SWc?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3">
+        <v>58</v>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">Nvidia CEO sees Kazakhstan as potential AI hub for Europe</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-10-30T14:29Z</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Euronews</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E12" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Main C — active</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">C — active</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G12" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Central Asia</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr">
+      <c r="H12" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Asia &amp; Pacific</t>
         </is>
       </c>
-      <c r="I11" s="3" t="inlineStr">
+      <c r="I12" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Country / regional R&amp;I policy or strategic foresight</t>
         </is>
       </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="K11" s="3" t="inlineStr">
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Region: Central Asia; issue: Country / regional R&amp;I policy or strategic foresight</t>
         </is>
       </c>
-      <c r="L11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="M11" s="3" t="inlineStr">
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">This may affect European access, investment or capability-building in a technology that is becoming strategically important.</t>
         </is>
       </c>
-      <c r="N11" s="3" t="inlineStr">
+      <c r="N12" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">provisional</t>
         </is>
       </c>
-      <c r="O11" s="3" t="inlineStr">
+      <c r="O12" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Deep Scan not complete</t>
         </is>
       </c>
-      <c r="P11" s="3" t="inlineStr">
+      <c r="P12" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Not verified + retained</t>
         </is>
       </c>
-      <c r="Q11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="R11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="S11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="T11" s="3" t="inlineStr">
+      <c r="Q12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T12" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">https://news.google.com/rss/articles/CBMimAFBVV95cUxQLUU2cGstT1FNbHpBb09nZVJ3a0xSMmNENmhCMWJnMFh6MXI2Nkhld2ZSWU5uM2Rmd3ZVdGFPT1BKbmVKN1d2M0dLcFdQWm5mT2ZNNDAxdnozSkxCdDZSel9YUGMtdnRTeHNya3l4RmFHOGNCeXVHOW9uM1VPcUo1dUQtZFpnSzJGNlFjLUY0Q1RpcWh3ZFFEbw?oc=5</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T11"/>
+  <autoFilter ref="A1:T12"/>
 </worksheet>
 </file>
 
@@ -48618,7 +48718,7 @@
         <v>3</v>
       </c>
       <c r="E59" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
@@ -48639,7 +48739,7 @@
         <v>0</v>
       </c>
       <c r="E60" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -48833,7 +48933,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-31T13:19:01+00:00</t>
+          <t xml:space="preserve">2026-10-31T15:07:25+00:00</t>
         </is>
       </c>
     </row>
@@ -48864,7 +48964,7 @@
         </is>
       </c>
       <c r="B6" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
@@ -49030,7 +49130,7 @@
         </is>
       </c>
       <c r="B3" s="3">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="4">
@@ -49060,7 +49160,7 @@
         </is>
       </c>
       <c r="B6" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
@@ -49070,7 +49170,7 @@
         </is>
       </c>
       <c r="B7" s="3">
-        <v>3623</v>
+        <v>3627</v>
       </c>
     </row>
     <row r="8">
@@ -49112,7 +49212,7 @@
         </is>
       </c>
       <c r="B11" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12">
@@ -49142,7 +49242,7 @@
         </is>
       </c>
       <c r="B14" s="3">
-        <v>505</v>
+        <v>508</v>
       </c>
     </row>
     <row r="15">
@@ -49152,7 +49252,7 @@
         </is>
       </c>
       <c r="B15" s="3">
-        <v>766</v>
+        <v>769</v>
       </c>
     </row>
     <row r="16">
@@ -49182,7 +49282,7 @@
         </is>
       </c>
       <c r="B18" s="3">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="19">
@@ -49192,7 +49292,7 @@
         </is>
       </c>
       <c r="B19" s="3">
-        <v>757</v>
+        <v>758</v>
       </c>
     </row>
     <row r="20">
@@ -49202,7 +49302,7 @@
         </is>
       </c>
       <c r="B20" s="3">
-        <v>1089</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="21">
@@ -49212,7 +49312,7 @@
         </is>
       </c>
       <c r="B21" s="3">
-        <v>4560</v>
+        <v>4566</v>
       </c>
     </row>
     <row r="22">
@@ -49342,7 +49442,7 @@
         </is>
       </c>
       <c r="B34" s="3">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="35">
@@ -49352,7 +49452,7 @@
         </is>
       </c>
       <c r="B35" s="3">
-        <v>3623</v>
+        <v>3627</v>
       </c>
     </row>
     <row r="36">

--- a/Relevance Stuff/relevance_stuff.xlsx
+++ b/Relevance Stuff/relevance_stuff.xlsx
@@ -46767,17 +46767,17 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">China’s Overlooked AI Strategy | Center for Security and Emerging Technology</t>
+          <t xml:space="preserve">The U.S.-China Technology War and Taiwan's Semiconductor Role in Geopolitics - HCSS</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-07-25</t>
+          <t xml:space="preserve">2023-11-20</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CSET</t>
+          <t xml:space="preserve">The Hague Centre for Strategic Studies</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -46807,7 +46807,7 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Foreign-affairs / trade / non-research ministries</t>
+          <t xml:space="preserve">Business / industry</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
@@ -46817,12 +46817,12 @@
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">The place to find CSET's publications, reports, and people In The News China’s Overlooked AI Strategy Foreign Affairs July 25, 2025 Owen J.</t>
+          <t xml:space="preserve">In the dynamic landscape of global geopolitics, Taiwan has emerged as a pivotal player in the U.S.-China technology war, particularly in the realm of semiconductor production.</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">This bears on Europe's research and innovation position. It is useful history for judging which earlier pressures still matter now.</t>
+          <t xml:space="preserve">This bears on Europe's ability to turn research into firms, production and scale. It is useful history for judging where European gains still depended on outside capital, technology, markets or access.</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
@@ -46857,7 +46857,7 @@
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://cset.georgetown.edu/article/chinas-overlooked-ai-strategy/</t>
+          <t xml:space="preserve">https://hcss.nl/wp-content/uploads/2023/11/The-US-China-Technology-War-and-Taiwans-Semiconductor-Role-Jiann-Chyuan-Wang-HCSS-2023.pdf</t>
         </is>
       </c>
     </row>
@@ -46867,17 +46867,17 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pursuing practicality and autonomy in the Indo-Pacific: the case of ROK-India Special Strategic Partnership</t>
+          <t xml:space="preserve">China’s Overlooked AI Strategy | Center for Security and Emerging Technology</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-15</t>
+          <t xml:space="preserve">2025-07-25</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asia Europe Journal</t>
+          <t xml:space="preserve">CSET</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -46892,7 +46892,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">India</t>
+          <t xml:space="preserve">China</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
@@ -46907,17 +46907,17 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Foreign-affairs / trade / non-research ministries</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Region: India; issue: Country / regional R&amp;I policy or strategic foresight</t>
+          <t xml:space="preserve">Region: China; issue: Country / regional R&amp;I policy or strategic foresight</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">The Indo-Pacific theater is emerging as a region that calls for complex geostrategic calculations.</t>
+          <t xml:space="preserve">The place to find CSET's publications, reports, and people In The News China’s Overlooked AI Strategy Foreign Affairs July 25, 2025 Owen J.</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
@@ -46952,32 +46952,32 @@
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hyun Ji Rim</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://doi.org/10.1007/s10308-025-00768-7</t>
+          <t xml:space="preserve">https://cset.georgetown.edu/article/chinas-overlooked-ai-strategy/</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ASEAN’s flagship universities and regional integration initiatives</t>
+          <t xml:space="preserve">Artificial Intelligence, Strategic Foresight, and Competitive Intelligence: Towards Convergence for Morocco’s Augmented Competitiveness</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2017-12-04</t>
+          <t xml:space="preserve">2025-11-04</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Higher Education</t>
+          <t xml:space="preserve">Governance</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -46987,42 +46987,42 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">B</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ASEAN</t>
+          <t xml:space="preserve">Morocco</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asia &amp; Pacific</t>
+          <t xml:space="preserve">Africa</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transnational R&amp;I and innovation policy</t>
+          <t xml:space="preserve">Country / regional R&amp;I policy or strategic foresight</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Universities / research institutions</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Region: ASEAN; issue: Transnational R&amp;I and innovation policy</t>
+          <t xml:space="preserve">Region: Morocco; issue: Country / regional R&amp;I policy or strategic foresight</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Purpose The purpose of this paper is to examine the role of Association of Southeast Asian Nations’ (ASEAN) flagship universities in moving the agenda of regional integration forward through academic/research collaboration and cooperation.</t>
+          <t xml:space="preserve">This paper explores how Artificial Intelligence, Strategic Foresight and Competitive Intelligence convergence can significantly contribute to enhancing Morocco’s national competitiveness, transformational growth, and consequently, placing the new development model within a new AI-driven paradigm by converging different intellige…</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">This bears on Europe's research workforce, skills and know-how. It is useful history for judging whether later policy really built durable European strength.</t>
+          <t xml:space="preserve">This bears on Europe's research and innovation position. It is useful history for judging which earlier pressures still matter now.</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
@@ -47052,32 +47052,32 @@
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Morshidi Sirat</t>
+          <t xml:space="preserve">Abdelmjid Lafram; Salah Eddine Bahji</t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://doi.org/10.1108/heed-07-2017-0004</t>
+          <t xml:space="preserve">https://doi.org/10.34190/ecmlg.21.1.4130</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">The data quagmire for German carmakers in China</t>
+          <t xml:space="preserve">Pursuing practicality and autonomy in the Indo-Pacific: the case of ROK-India Special Strategic Partnership</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-05-06</t>
+          <t xml:space="preserve">2025-12-15</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">MERICS</t>
+          <t xml:space="preserve">Asia Europe Journal</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -47092,7 +47092,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">China</t>
+          <t xml:space="preserve">India</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
@@ -47107,22 +47107,22 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business / industry</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Region: China; issue: Country / regional R&amp;I policy or strategic foresight</t>
+          <t xml:space="preserve">Region: India; issue: Country / regional R&amp;I policy or strategic foresight</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">The renewal of the Sino-German MoU on autonomous vehicles opens up questions around data privacy, security, and Germany’s industrial competitiveness, says Rebecca Arcesati.</t>
+          <t xml:space="preserve">The Indo-Pacific theater is emerging as a region that calls for complex geostrategic calculations.</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">This bears on Europe's ability to turn research into firms, production and scale. It is useful history for judging where European gains still depended on outside capital, technology, markets or access.</t>
+          <t xml:space="preserve">This bears on Europe's research and innovation position. It is useful history for judging which earlier pressures still matter now.</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
@@ -47152,12 +47152,12 @@
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Hyun Ji Rim</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://merics.org/en/comment/data-quagmire-german-carmakers-china</t>
+          <t xml:space="preserve">https://doi.org/10.1007/s10308-025-00768-7</t>
         </is>
       </c>
     </row>
@@ -47167,67 +47167,67 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">EU can compete with US AI giants, says Brussels’ frontier-model champion</t>
+          <t xml:space="preserve">ASEAN’s flagship universities and regional integration initiatives</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-29T06:00Z</t>
+          <t xml:space="preserve">2017-12-04</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Financial Times</t>
+          <t xml:space="preserve">Higher Education</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Main C — active</t>
+          <t xml:space="preserve">Historical</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">C — active</t>
+          <t xml:space="preserve">A</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">United States</t>
+          <t xml:space="preserve">ASEAN</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Americas</t>
+          <t xml:space="preserve">Asia &amp; Pacific</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Country / regional R&amp;I policy or strategic foresight</t>
+          <t xml:space="preserve">Transnational R&amp;I and innovation policy</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Universities / research institutions</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Region: United States; issue: Country / regional R&amp;I policy or strategic foresight</t>
+          <t xml:space="preserve">Region: ASEAN; issue: Transnational R&amp;I and innovation policy</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Purpose The purpose of this paper is to examine the role of Association of Southeast Asian Nations’ (ASEAN) flagship universities in moving the agenda of regional integration forward through academic/research collaboration and cooperation.</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">This may affect European access, investment or capability-building in a technology that is becoming strategically important.</t>
+          <t xml:space="preserve">This bears on Europe's research workforce, skills and know-how. It is useful history for judging whether later policy really built durable European strength.</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">provisional</t>
+          <t xml:space="preserve">not yet checked</t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
@@ -47252,12 +47252,12 @@
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Morshidi Sirat</t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://news.google.com/rss/articles/CBMihAFBVV95cUxNNE0tYWZuVElPc1pqVXdBNjFpX3AwcDM4SEpWangyang0ZlZsb21TR0EtVzAyZlBaNk9mVzRqdEgyMXRaS3Brd1ZIZnpvTHJONEd6dXBiWm1LakY3eXMzN3hXZ0szQ0w4UDZBTmFjTmc4UV9xWjlqMUFHZTdoSGZwSE5GVHk?oc=5</t>
+          <t xml:space="preserve">https://doi.org/10.1108/heed-07-2017-0004</t>
         </is>
       </c>
     </row>
@@ -47267,37 +47267,37 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">How Africa-Europe research is changing global health</t>
+          <t xml:space="preserve">The data quagmire for German carmakers in China</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-29T12:28Z</t>
+          <t xml:space="preserve">2024-05-06</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Science|Business</t>
+          <t xml:space="preserve">MERICS</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Main C — active</t>
+          <t xml:space="preserve">Historical</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">C — active</t>
+          <t xml:space="preserve">A</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Africa (region)</t>
+          <t xml:space="preserve">China</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Africa</t>
+          <t xml:space="preserve">Asia &amp; Pacific</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -47307,27 +47307,27 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Business / industry</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Region: Africa (region); issue: Country / regional R&amp;I policy or strategic foresight</t>
+          <t xml:space="preserve">Region: China; issue: Country / regional R&amp;I policy or strategic foresight</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">The renewal of the Sino-German MoU on autonomous vehicles opens up questions around data privacy, security, and Germany’s industrial competitiveness, says Rebecca Arcesati.</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">This may change Europe's relative research and innovation capacity in technologies that increasingly shape geopolitical power.</t>
+          <t xml:space="preserve">This bears on Europe's ability to turn research into firms, production and scale. It is useful history for judging where European gains still depended on outside capital, technology, markets or access.</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">provisional</t>
+          <t xml:space="preserve">not yet checked</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
@@ -47357,7 +47357,7 @@
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://news.google.com/rss/articles/CBMiigFBVV95cUxPZjRtYTlLZU4tRTU0S0VJdkZZZmZIR29PSFdzQUJPdWJnTGVNY2lmdHpRaUVqQzdrTFF2U0xpXzZZb0JLdDNUNkdUQllCZnJXX0tiLVc1VWJHd1lEMXpadHlXZGRWTTdDdGw1eWZmM3RUZjItV1BRbUNIZTJsdWRiZ0RUY25JODA4SWc?oc=5</t>
+          <t xml:space="preserve">https://merics.org/en/comment/data-quagmire-german-carmakers-china</t>
         </is>
       </c>
     </row>
@@ -47367,102 +47367,302 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">EU can compete with US AI giants, says Brussels’ frontier-model champion</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-29T06:00Z</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Financial Times</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Main C — active</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C — active</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">United States</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Americas</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Country / regional R&amp;I policy or strategic foresight</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Region: United States; issue: Country / regional R&amp;I policy or strategic foresight</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">This may affect European access, investment or capability-building in a technology that is becoming strategically important.</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">provisional</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Deep Scan not complete</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not verified + retained</t>
+        </is>
+      </c>
+      <c r="Q12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://news.google.com/rss/articles/CBMihAFBVV95cUxNNE0tYWZuVElPc1pqVXdBNjFpX3AwcDM4SEpWangyang0ZlZsb21TR0EtVzAyZlBaNk9mVzRqdEgyMXRaS3Brd1ZIZnpvTHJONEd6dXBiWm1LakY3eXMzN3hXZ0szQ0w4UDZBTmFjTmc4UV9xWjlqMUFHZTdoSGZwSE5GVHk?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3">
+        <v>58</v>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">How Africa-Europe research is changing global health</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-29T12:28Z</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Science|Business</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Main C — active</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C — active</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Africa (region)</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Africa</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Country / regional R&amp;I policy or strategic foresight</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Region: Africa (region); issue: Country / regional R&amp;I policy or strategic foresight</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">This may change Europe's relative research and innovation capacity in technologies that increasingly shape geopolitical power.</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">provisional</t>
+        </is>
+      </c>
+      <c r="O13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Deep Scan not complete</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not verified + retained</t>
+        </is>
+      </c>
+      <c r="Q13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://news.google.com/rss/articles/CBMiigFBVV95cUxPZjRtYTlLZU4tRTU0S0VJdkZZZmZIR29PSFdzQUJPdWJnTGVNY2lmdHpRaUVqQzdrTFF2U0xpXzZZb0JLdDNUNkdUQllCZnJXX0tiLVc1VWJHd1lEMXpadHlXZGRWTTdDdGw1eWZmM3RUZjItV1BRbUNIZTJsdWRiZ0RUY25JODA4SWc?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3">
+        <v>58</v>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">Nvidia CEO sees Kazakhstan as potential AI hub for Europe</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-10-30T14:29Z</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Euronews</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="E14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Main C — active</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="F14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">C — active</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="G14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Central Asia</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr">
+      <c r="H14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Asia &amp; Pacific</t>
         </is>
       </c>
-      <c r="I12" s="3" t="inlineStr">
+      <c r="I14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Country / regional R&amp;I policy or strategic foresight</t>
         </is>
       </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="K12" s="3" t="inlineStr">
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Region: Central Asia; issue: Country / regional R&amp;I policy or strategic foresight</t>
         </is>
       </c>
-      <c r="L12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="M12" s="3" t="inlineStr">
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">This may affect European access, investment or capability-building in a technology that is becoming strategically important.</t>
         </is>
       </c>
-      <c r="N12" s="3" t="inlineStr">
+      <c r="N14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">provisional</t>
         </is>
       </c>
-      <c r="O12" s="3" t="inlineStr">
+      <c r="O14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Deep Scan not complete</t>
         </is>
       </c>
-      <c r="P12" s="3" t="inlineStr">
+      <c r="P14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Not verified + retained</t>
         </is>
       </c>
-      <c r="Q12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="R12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="S12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="T12" s="3" t="inlineStr">
+      <c r="Q14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">https://news.google.com/rss/articles/CBMimAFBVV95cUxQLUU2cGstT1FNbHpBb09nZVJ3a0xSMmNENmhCMWJnMFh6MXI2Nkhld2ZSWU5uM2Rmd3ZVdGFPT1BKbmVKN1d2M0dLcFdQWm5mT2ZNNDAxdnozSkxCdDZSel9YUGMtdnRTeHNya3l4RmFHOGNCeXVHOW9uM1VPcUo1dUQtZFpnSzJGNlFjLUY0Q1RpcWh3ZFFEbw?oc=5</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T12"/>
+  <autoFilter ref="A1:T14"/>
 </worksheet>
 </file>
 
@@ -47983,7 +48183,7 @@
         <v>0</v>
       </c>
       <c r="E24" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -48235,7 +48435,7 @@
         <v>7</v>
       </c>
       <c r="E36" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="37">
@@ -48466,7 +48666,7 @@
         <v>1</v>
       </c>
       <c r="E47" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48">
@@ -48487,7 +48687,7 @@
         <v>7</v>
       </c>
       <c r="E48" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="49">
@@ -48781,7 +48981,7 @@
         <v>5</v>
       </c>
       <c r="E62" s="3">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="63">
@@ -48844,7 +49044,7 @@
         <v>5</v>
       </c>
       <c r="E65" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66">
@@ -48933,7 +49133,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-31T15:07:25+00:00</t>
+          <t xml:space="preserve">2026-10-31T16:42:43+00:00</t>
         </is>
       </c>
     </row>
@@ -48964,7 +49164,7 @@
         </is>
       </c>
       <c r="B6" s="3">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7">
@@ -49130,7 +49330,7 @@
         </is>
       </c>
       <c r="B3" s="3">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="4">
@@ -49160,7 +49360,7 @@
         </is>
       </c>
       <c r="B6" s="3">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7">
@@ -49170,7 +49370,7 @@
         </is>
       </c>
       <c r="B7" s="3">
-        <v>3627</v>
+        <v>3631</v>
       </c>
     </row>
     <row r="8">
@@ -49190,7 +49390,7 @@
         </is>
       </c>
       <c r="B9" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10">
@@ -49212,7 +49412,7 @@
         </is>
       </c>
       <c r="B11" s="3">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12">
@@ -49232,7 +49432,7 @@
         </is>
       </c>
       <c r="B13" s="3">
-        <v>1886</v>
+        <v>1890</v>
       </c>
     </row>
     <row r="14">
@@ -49302,7 +49502,7 @@
         </is>
       </c>
       <c r="B20" s="3">
-        <v>1091</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="21">
@@ -49312,7 +49512,7 @@
         </is>
       </c>
       <c r="B21" s="3">
-        <v>4566</v>
+        <v>4568</v>
       </c>
     </row>
     <row r="22">
@@ -49442,7 +49642,7 @@
         </is>
       </c>
       <c r="B34" s="3">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="35">
@@ -49452,7 +49652,7 @@
         </is>
       </c>
       <c r="B35" s="3">
-        <v>3627</v>
+        <v>3631</v>
       </c>
     </row>
     <row r="36">
@@ -49530,7 +49730,7 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zero coverage: Morocco</t>
+          <t xml:space="preserve">Zero coverage: Nigeria</t>
         </is>
       </c>
       <c r="B43" s="3">
@@ -49540,7 +49740,7 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zero coverage: Nigeria</t>
+          <t xml:space="preserve">Zero coverage: Rwanda</t>
         </is>
       </c>
       <c r="B44" s="3">
@@ -49550,7 +49750,7 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zero coverage: Rwanda</t>
+          <t xml:space="preserve">Zero coverage: South Africa</t>
         </is>
       </c>
       <c r="B45" s="3">
@@ -49560,7 +49760,7 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zero coverage: South Africa</t>
+          <t xml:space="preserve">Zero coverage: Palestine</t>
         </is>
       </c>
       <c r="B46" s="3">
@@ -49570,7 +49770,7 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zero coverage: Palestine</t>
+          <t xml:space="preserve">Zero coverage: Jordan</t>
         </is>
       </c>
       <c r="B47" s="3">
@@ -49580,24 +49780,14 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zero coverage: Jordan</t>
+          <t xml:space="preserve">Zero coverage: Saudi Arabia</t>
         </is>
       </c>
       <c r="B48" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Zero coverage: Saudi Arabia</t>
-        </is>
-      </c>
-      <c r="B49" s="3">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:B49"/>
+  <autoFilter ref="A1:B48"/>
 </worksheet>
 </file>
--- a/Relevance Stuff/relevance_stuff.xlsx
+++ b/Relevance Stuff/relevance_stuff.xlsx
@@ -47163,71 +47163,71 @@
     </row>
     <row r="10">
       <c r="A10" s="3">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ASEAN’s flagship universities and regional integration initiatives</t>
+          <t xml:space="preserve">EU and Canada team up in supercomputing and quantum - Shaping Europe’s digital future</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2017-12-04</t>
+          <t xml:space="preserve">2026-10-31T00:06Z</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Higher Education</t>
+          <t xml:space="preserve">EU Digital Strategy</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Historical</t>
+          <t xml:space="preserve">Main C — active</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">C — active</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ASEAN</t>
+          <t xml:space="preserve">Canada</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asia &amp; Pacific</t>
+          <t xml:space="preserve">Americas</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transnational R&amp;I and innovation policy</t>
+          <t xml:space="preserve">Country / regional R&amp;I policy or strategic foresight</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Universities / research institutions</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Region: ASEAN; issue: Transnational R&amp;I and innovation policy</t>
+          <t xml:space="preserve">Region: Canada; issue: Country / regional R&amp;I policy or strategic foresight</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Purpose The purpose of this paper is to examine the role of Association of Southeast Asian Nations’ (ASEAN) flagship universities in moving the agenda of regional integration forward through academic/research collaboration and cooperation.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">This bears on Europe's research workforce, skills and know-how. It is useful history for judging whether later policy really built durable European strength.</t>
+          <t xml:space="preserve">This may affect European access, investment or capability-building in a technology that is becoming strategically important.</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">not yet checked</t>
+          <t xml:space="preserve">provisional</t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
@@ -47252,12 +47252,12 @@
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Morshidi Sirat</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://doi.org/10.1108/heed-07-2017-0004</t>
+          <t xml:space="preserve">https://news.google.com/rss/articles/CBMilgFBVV95cUxQQWdpRTZpY2tMenMwb3ltOFIycHd0MC1nWEpZMjFuR3VpWnBoVlg5anhZdDBqLVBCOThuOVEweWFRaU01Rjh2NGtLalhzbFBaU0d4WV9paWpQZmZfWlRGSEhnZmJhRkpPeFRmYUlvSkZHcmV4N3hOUnQyQVNmWW1qc3NSdzkzdi1UR3N6emdISmpnY3hXQUE?oc=5</t>
         </is>
       </c>
     </row>
@@ -47267,17 +47267,17 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">The data quagmire for German carmakers in China</t>
+          <t xml:space="preserve">ASEAN’s flagship universities and regional integration initiatives</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-05-06</t>
+          <t xml:space="preserve">2017-12-04</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">MERICS</t>
+          <t xml:space="preserve">Higher Education</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -47292,7 +47292,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">China</t>
+          <t xml:space="preserve">ASEAN</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
@@ -47302,27 +47302,27 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Country / regional R&amp;I policy or strategic foresight</t>
+          <t xml:space="preserve">Transnational R&amp;I and innovation policy</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business / industry</t>
+          <t xml:space="preserve">Universities / research institutions</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Region: China; issue: Country / regional R&amp;I policy or strategic foresight</t>
+          <t xml:space="preserve">Region: ASEAN; issue: Transnational R&amp;I and innovation policy</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">The renewal of the Sino-German MoU on autonomous vehicles opens up questions around data privacy, security, and Germany’s industrial competitiveness, says Rebecca Arcesati.</t>
+          <t xml:space="preserve">Purpose The purpose of this paper is to examine the role of Association of Southeast Asian Nations’ (ASEAN) flagship universities in moving the agenda of regional integration forward through academic/research collaboration and cooperation.</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">This bears on Europe's ability to turn research into firms, production and scale. It is useful history for judging where European gains still depended on outside capital, technology, markets or access.</t>
+          <t xml:space="preserve">This bears on Europe's research workforce, skills and know-how. It is useful history for judging whether later policy really built durable European strength.</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
@@ -47352,12 +47352,12 @@
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Morshidi Sirat</t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://merics.org/en/comment/data-quagmire-german-carmakers-china</t>
+          <t xml:space="preserve">https://doi.org/10.1108/heed-07-2017-0004</t>
         </is>
       </c>
     </row>
@@ -47367,37 +47367,37 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">EU can compete with US AI giants, says Brussels’ frontier-model champion</t>
+          <t xml:space="preserve">The data quagmire for German carmakers in China</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-29T06:00Z</t>
+          <t xml:space="preserve">2024-05-06</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Financial Times</t>
+          <t xml:space="preserve">MERICS</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Main C — active</t>
+          <t xml:space="preserve">Historical</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">C — active</t>
+          <t xml:space="preserve">A</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">United States</t>
+          <t xml:space="preserve">China</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Americas</t>
+          <t xml:space="preserve">Asia &amp; Pacific</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
@@ -47407,27 +47407,27 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Business / industry</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Region: United States; issue: Country / regional R&amp;I policy or strategic foresight</t>
+          <t xml:space="preserve">Region: China; issue: Country / regional R&amp;I policy or strategic foresight</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">The renewal of the Sino-German MoU on autonomous vehicles opens up questions around data privacy, security, and Germany’s industrial competitiveness, says Rebecca Arcesati.</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">This may affect European access, investment or capability-building in a technology that is becoming strategically important.</t>
+          <t xml:space="preserve">This bears on Europe's ability to turn research into firms, production and scale. It is useful history for judging where European gains still depended on outside capital, technology, markets or access.</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">provisional</t>
+          <t xml:space="preserve">not yet checked</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
@@ -47457,7 +47457,7 @@
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://news.google.com/rss/articles/CBMihAFBVV95cUxNNE0tYWZuVElPc1pqVXdBNjFpX3AwcDM4SEpWangyang0ZlZsb21TR0EtVzAyZlBaNk9mVzRqdEgyMXRaS3Brd1ZIZnpvTHJONEd6dXBiWm1LakY3eXMzN3hXZ0szQ0w4UDZBTmFjTmc4UV9xWjlqMUFHZTdoSGZwSE5GVHk?oc=5</t>
+          <t xml:space="preserve">https://merics.org/en/comment/data-quagmire-german-carmakers-china</t>
         </is>
       </c>
     </row>
@@ -47467,17 +47467,17 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">How Africa-Europe research is changing global health</t>
+          <t xml:space="preserve">EU can compete with US AI giants, says Brussels’ frontier-model champion</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-29T12:28Z</t>
+          <t xml:space="preserve">2026-10-29T06:00Z</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Science|Business</t>
+          <t xml:space="preserve">Financial Times</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -47492,12 +47492,12 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Africa (region)</t>
+          <t xml:space="preserve">United States</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Africa</t>
+          <t xml:space="preserve">Americas</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
@@ -47512,7 +47512,7 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Region: Africa (region); issue: Country / regional R&amp;I policy or strategic foresight</t>
+          <t xml:space="preserve">Region: United States; issue: Country / regional R&amp;I policy or strategic foresight</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
@@ -47522,7 +47522,7 @@
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">This may change Europe's relative research and innovation capacity in technologies that increasingly shape geopolitical power.</t>
+          <t xml:space="preserve">This may affect European access, investment or capability-building in a technology that is becoming strategically important.</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
@@ -47557,7 +47557,7 @@
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://news.google.com/rss/articles/CBMiigFBVV95cUxPZjRtYTlLZU4tRTU0S0VJdkZZZmZIR29PSFdzQUJPdWJnTGVNY2lmdHpRaUVqQzdrTFF2U0xpXzZZb0JLdDNUNkdUQllCZnJXX0tiLVc1VWJHd1lEMXpadHlXZGRWTTdDdGw1eWZmM3RUZjItV1BRbUNIZTJsdWRiZ0RUY25JODA4SWc?oc=5</t>
+          <t xml:space="preserve">https://news.google.com/rss/articles/CBMihAFBVV95cUxNNE0tYWZuVElPc1pqVXdBNjFpX3AwcDM4SEpWangyang0ZlZsb21TR0EtVzAyZlBaNk9mVzRqdEgyMXRaS3Brd1ZIZnpvTHJONEd6dXBiWm1LakY3eXMzN3hXZ0szQ0w4UDZBTmFjTmc4UV9xWjlqMUFHZTdoSGZwSE5GVHk?oc=5</t>
         </is>
       </c>
     </row>
@@ -47567,102 +47567,202 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">How Africa-Europe research is changing global health</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-29T12:28Z</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Science|Business</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Main C — active</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C — active</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Africa (region)</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Africa</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Country / regional R&amp;I policy or strategic foresight</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Region: Africa (region); issue: Country / regional R&amp;I policy or strategic foresight</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">This may change Europe's relative research and innovation capacity in technologies that increasingly shape geopolitical power.</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">provisional</t>
+        </is>
+      </c>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Deep Scan not complete</t>
+        </is>
+      </c>
+      <c r="P14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not verified + retained</t>
+        </is>
+      </c>
+      <c r="Q14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://news.google.com/rss/articles/CBMiigFBVV95cUxPZjRtYTlLZU4tRTU0S0VJdkZZZmZIR29PSFdzQUJPdWJnTGVNY2lmdHpRaUVqQzdrTFF2U0xpXzZZb0JLdDNUNkdUQllCZnJXX0tiLVc1VWJHd1lEMXpadHlXZGRWTTdDdGw1eWZmM3RUZjItV1BRbUNIZTJsdWRiZ0RUY25JODA4SWc?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3">
+        <v>58</v>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">Nvidia CEO sees Kazakhstan as potential AI hub for Europe</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-10-30T14:29Z</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Euronews</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Main C — active</t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">C — active</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="G15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Central Asia</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr">
+      <c r="H15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Asia &amp; Pacific</t>
         </is>
       </c>
-      <c r="I14" s="3" t="inlineStr">
+      <c r="I15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Country / regional R&amp;I policy or strategic foresight</t>
         </is>
       </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="K14" s="3" t="inlineStr">
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Region: Central Asia; issue: Country / regional R&amp;I policy or strategic foresight</t>
         </is>
       </c>
-      <c r="L14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="M14" s="3" t="inlineStr">
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">This may affect European access, investment or capability-building in a technology that is becoming strategically important.</t>
         </is>
       </c>
-      <c r="N14" s="3" t="inlineStr">
+      <c r="N15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">provisional</t>
         </is>
       </c>
-      <c r="O14" s="3" t="inlineStr">
+      <c r="O15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Deep Scan not complete</t>
         </is>
       </c>
-      <c r="P14" s="3" t="inlineStr">
+      <c r="P15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Not verified + retained</t>
         </is>
       </c>
-      <c r="Q14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="R14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="S14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="T14" s="3" t="inlineStr">
+      <c r="Q15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">https://news.google.com/rss/articles/CBMimAFBVV95cUxQLUU2cGstT1FNbHpBb09nZVJ3a0xSMmNENmhCMWJnMFh6MXI2Nkhld2ZSWU5uM2Rmd3ZVdGFPT1BKbmVKN1d2M0dLcFdQWm5mT2ZNNDAxdnozSkxCdDZSel9YUGMtdnRTeHNya3l4RmFHOGNCeXVHOW9uM1VPcUo1dUQtZFpnSzJGNlFjLUY0Q1RpcWh3ZFFEbw?oc=5</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T14"/>
+  <autoFilter ref="A1:T15"/>
 </worksheet>
 </file>
 
@@ -47973,7 +48073,7 @@
         <v>2</v>
       </c>
       <c r="E14" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -48645,7 +48745,7 @@
         <v>9</v>
       </c>
       <c r="E46" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47">
@@ -48981,7 +49081,7 @@
         <v>5</v>
       </c>
       <c r="E62" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="63">
@@ -49133,7 +49233,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-31T16:42:43+00:00</t>
+          <t xml:space="preserve">2026-10-31T20:42:44+00:00</t>
         </is>
       </c>
     </row>
@@ -49164,7 +49264,7 @@
         </is>
       </c>
       <c r="B6" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7">
@@ -49330,7 +49430,7 @@
         </is>
       </c>
       <c r="B3" s="3">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="4">
@@ -49360,7 +49460,7 @@
         </is>
       </c>
       <c r="B6" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7">
@@ -49370,7 +49470,7 @@
         </is>
       </c>
       <c r="B7" s="3">
-        <v>3631</v>
+        <v>3634</v>
       </c>
     </row>
     <row r="8">
@@ -49412,7 +49512,7 @@
         </is>
       </c>
       <c r="B11" s="3">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12">
@@ -49442,7 +49542,7 @@
         </is>
       </c>
       <c r="B14" s="3">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="15">
@@ -49452,7 +49552,7 @@
         </is>
       </c>
       <c r="B15" s="3">
-        <v>769</v>
+        <v>770</v>
       </c>
     </row>
     <row r="16">
@@ -49482,7 +49582,7 @@
         </is>
       </c>
       <c r="B18" s="3">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="19">
@@ -49492,7 +49592,7 @@
         </is>
       </c>
       <c r="B19" s="3">
-        <v>758</v>
+        <v>760</v>
       </c>
     </row>
     <row r="20">
@@ -49502,7 +49602,7 @@
         </is>
       </c>
       <c r="B20" s="3">
-        <v>1093</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="21">
@@ -49512,7 +49612,7 @@
         </is>
       </c>
       <c r="B21" s="3">
-        <v>4568</v>
+        <v>4572</v>
       </c>
     </row>
     <row r="22">
@@ -49642,7 +49742,7 @@
         </is>
       </c>
       <c r="B34" s="3">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="35">
@@ -49652,7 +49752,7 @@
         </is>
       </c>
       <c r="B35" s="3">
-        <v>3631</v>
+        <v>3634</v>
       </c>
     </row>
     <row r="36">
